--- a/Rotation-3-Thermodynamics/Sample-Data/Adiabatic_SampleData.xlsx
+++ b/Rotation-3-Thermodynamics/Sample-Data/Adiabatic_SampleData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prajay\Documents\GitHub\CHE-3131\Rotation-3-Thermodynamics\Sample-Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D054E6-9D2C-43EF-BE30-80CE2B141EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68999410-A0B3-4858-893F-B8904BA54786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Argon_Trial1" sheetId="3" r:id="rId1"/>
@@ -3945,7 +3945,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9237A350-E82A-422B-9D89-D90E90528521}">
-  <dimension ref="A1:D348"/>
+  <dimension ref="A1:D248"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -3967,13 +3967,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>21.36</v>
+        <v>21.08</v>
       </c>
       <c r="C2">
-        <v>103.142</v>
+        <v>102.17400000000001</v>
       </c>
       <c r="D2">
-        <v>103.06399999999999</v>
+        <v>102.095</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -3981,13 +3981,13 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>21.36</v>
+        <v>21.11</v>
       </c>
       <c r="C3">
-        <v>103.142</v>
+        <v>102.211</v>
       </c>
       <c r="D3">
-        <v>103.101</v>
+        <v>102.133</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -3995,13 +3995,13 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>21.36</v>
+        <v>21.11</v>
       </c>
       <c r="C4">
-        <v>103.142</v>
+        <v>102.211</v>
       </c>
       <c r="D4">
-        <v>103.101</v>
+        <v>102.17</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -4009,13 +4009,13 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>21.39</v>
+        <v>21.08</v>
       </c>
       <c r="C5">
-        <v>103.105</v>
+        <v>102.249</v>
       </c>
       <c r="D5">
-        <v>103.101</v>
+        <v>102.17</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -4023,13 +4023,13 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>21.36</v>
+        <v>21.11</v>
       </c>
       <c r="C6">
-        <v>103.142</v>
+        <v>102.286</v>
       </c>
       <c r="D6">
-        <v>103.101</v>
+        <v>102.20699999999999</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -4037,13 +4037,13 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>21.36</v>
+        <v>21.11</v>
       </c>
       <c r="C7">
-        <v>103.142</v>
+        <v>102.286</v>
       </c>
       <c r="D7">
-        <v>103.06399999999999</v>
+        <v>102.244</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -4051,13 +4051,13 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>21.36</v>
+        <v>21.13</v>
       </c>
       <c r="C8">
-        <v>103.105</v>
+        <v>102.249</v>
       </c>
       <c r="D8">
-        <v>103.101</v>
+        <v>102.244</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -4065,13 +4065,13 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>21.36</v>
+        <v>21.16</v>
       </c>
       <c r="C9">
-        <v>103.105</v>
+        <v>102.32299999999999</v>
       </c>
       <c r="D9">
-        <v>103.101</v>
+        <v>102.282</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -4079,13 +4079,13 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>21.39</v>
+        <v>21.18</v>
       </c>
       <c r="C10">
-        <v>103.105</v>
+        <v>102.32299999999999</v>
       </c>
       <c r="D10">
-        <v>103.101</v>
+        <v>102.282</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -4093,13 +4093,13 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>21.36</v>
+        <v>21.18</v>
       </c>
       <c r="C11">
-        <v>103.179</v>
+        <v>102.36</v>
       </c>
       <c r="D11">
-        <v>103.06399999999999</v>
+        <v>102.282</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -4107,13 +4107,13 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>21.39</v>
+        <v>21.18</v>
       </c>
       <c r="C12">
-        <v>103.142</v>
+        <v>102.32299999999999</v>
       </c>
       <c r="D12">
-        <v>103.101</v>
+        <v>102.35599999999999</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -4121,13 +4121,13 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>21.39</v>
+        <v>21.21</v>
       </c>
       <c r="C13">
-        <v>103.179</v>
+        <v>102.36</v>
       </c>
       <c r="D13">
-        <v>103.101</v>
+        <v>102.319</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -4135,13 +4135,13 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>21.36</v>
+        <v>21.23</v>
       </c>
       <c r="C14">
-        <v>103.142</v>
+        <v>102.36</v>
       </c>
       <c r="D14">
-        <v>103.06399999999999</v>
+        <v>102.319</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -4149,13 +4149,13 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>21.41</v>
+        <v>21.23</v>
       </c>
       <c r="C15">
-        <v>103.142</v>
+        <v>102.36</v>
       </c>
       <c r="D15">
-        <v>103.06399999999999</v>
+        <v>102.319</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -4163,13 +4163,13 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>21.39</v>
+        <v>21.23</v>
       </c>
       <c r="C16">
-        <v>103.142</v>
+        <v>102.398</v>
       </c>
       <c r="D16">
-        <v>103.06399999999999</v>
+        <v>102.35599999999999</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -4177,13 +4177,13 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>21.39</v>
+        <v>21.28</v>
       </c>
       <c r="C17">
-        <v>103.142</v>
+        <v>102.398</v>
       </c>
       <c r="D17">
-        <v>103.06399999999999</v>
+        <v>102.35599999999999</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -4191,13 +4191,13 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>21.39</v>
+        <v>21.23</v>
       </c>
       <c r="C18">
-        <v>103.142</v>
+        <v>102.47199999999999</v>
       </c>
       <c r="D18">
-        <v>103.06399999999999</v>
+        <v>102.35599999999999</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -4205,13 +4205,13 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>21.39</v>
+        <v>21.26</v>
       </c>
       <c r="C19">
-        <v>103.179</v>
+        <v>102.36</v>
       </c>
       <c r="D19">
-        <v>103.06399999999999</v>
+        <v>102.35599999999999</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -4219,13 +4219,13 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>21.36</v>
+        <v>21.28</v>
       </c>
       <c r="C20">
-        <v>103.142</v>
+        <v>102.435</v>
       </c>
       <c r="D20">
-        <v>103.101</v>
+        <v>102.393</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -4233,13 +4233,13 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>21.39</v>
+        <v>21.31</v>
       </c>
       <c r="C21">
-        <v>103.142</v>
+        <v>102.398</v>
       </c>
       <c r="D21">
-        <v>103.101</v>
+        <v>102.393</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -4247,13 +4247,13 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>21.39</v>
+        <v>21.31</v>
       </c>
       <c r="C22">
-        <v>103.179</v>
+        <v>102.435</v>
       </c>
       <c r="D22">
-        <v>103.101</v>
+        <v>102.393</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -4261,13 +4261,13 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>21.36</v>
+        <v>21.28</v>
       </c>
       <c r="C23">
-        <v>103.142</v>
+        <v>102.435</v>
       </c>
       <c r="D23">
-        <v>103.101</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -4275,13 +4275,13 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>21.36</v>
+        <v>21.31</v>
       </c>
       <c r="C24">
-        <v>103.142</v>
+        <v>102.47199999999999</v>
       </c>
       <c r="D24">
-        <v>103.101</v>
+        <v>102.35599999999999</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -4289,13 +4289,13 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>21.36</v>
+        <v>21.34</v>
       </c>
       <c r="C25">
-        <v>103.142</v>
+        <v>102.47199999999999</v>
       </c>
       <c r="D25">
-        <v>103.101</v>
+        <v>102.393</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -4303,13 +4303,13 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>21.39</v>
+        <v>21.31</v>
       </c>
       <c r="C26">
-        <v>103.142</v>
+        <v>102.47199999999999</v>
       </c>
       <c r="D26">
-        <v>103.06399999999999</v>
+        <v>102.393</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -4317,13 +4317,13 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>21.39</v>
+        <v>21.34</v>
       </c>
       <c r="C27">
-        <v>103.142</v>
+        <v>102.47199999999999</v>
       </c>
       <c r="D27">
-        <v>103.101</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -4334,10 +4334,10 @@
         <v>21.34</v>
       </c>
       <c r="C28">
-        <v>103.105</v>
+        <v>102.509</v>
       </c>
       <c r="D28">
-        <v>103.06399999999999</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -4348,10 +4348,10 @@
         <v>21.34</v>
       </c>
       <c r="C29">
-        <v>103.142</v>
+        <v>102.509</v>
       </c>
       <c r="D29">
-        <v>103.101</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -4362,10 +4362,10 @@
         <v>21.36</v>
       </c>
       <c r="C30">
-        <v>103.142</v>
+        <v>102.47199999999999</v>
       </c>
       <c r="D30">
-        <v>103.06399999999999</v>
+        <v>102.468</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -4373,13 +4373,13 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>21.36</v>
+        <v>21.34</v>
       </c>
       <c r="C31">
-        <v>103.105</v>
+        <v>102.509</v>
       </c>
       <c r="D31">
-        <v>103.101</v>
+        <v>102.468</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -4390,10 +4390,10 @@
         <v>21.36</v>
       </c>
       <c r="C32">
-        <v>103.179</v>
+        <v>102.509</v>
       </c>
       <c r="D32">
-        <v>103.06399999999999</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -4404,10 +4404,10 @@
         <v>21.39</v>
       </c>
       <c r="C33">
-        <v>103.142</v>
+        <v>102.47199999999999</v>
       </c>
       <c r="D33">
-        <v>103.026</v>
+        <v>102.468</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -4415,13 +4415,13 @@
         <v>32</v>
       </c>
       <c r="B34">
-        <v>21.34</v>
+        <v>21.39</v>
       </c>
       <c r="C34">
-        <v>103.142</v>
+        <v>102.509</v>
       </c>
       <c r="D34">
-        <v>103.026</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -4432,10 +4432,10 @@
         <v>21.36</v>
       </c>
       <c r="C35">
-        <v>103.105</v>
+        <v>102.509</v>
       </c>
       <c r="D35">
-        <v>103.026</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -4446,10 +4446,10 @@
         <v>21.36</v>
       </c>
       <c r="C36">
-        <v>103.105</v>
+        <v>102.509</v>
       </c>
       <c r="D36">
-        <v>103.06399999999999</v>
+        <v>102.468</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -4460,10 +4460,10 @@
         <v>21.36</v>
       </c>
       <c r="C37">
-        <v>103.105</v>
+        <v>102.54600000000001</v>
       </c>
       <c r="D37">
-        <v>103.06399999999999</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -4471,13 +4471,13 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>21.36</v>
+        <v>21.39</v>
       </c>
       <c r="C38">
-        <v>103.142</v>
+        <v>102.54600000000001</v>
       </c>
       <c r="D38">
-        <v>103.06399999999999</v>
+        <v>102.468</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -4485,13 +4485,13 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>21.36</v>
+        <v>21.41</v>
       </c>
       <c r="C39">
-        <v>103.105</v>
+        <v>102.509</v>
       </c>
       <c r="D39">
-        <v>103.06399999999999</v>
+        <v>102.468</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -4499,13 +4499,13 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>21.34</v>
+        <v>21.41</v>
       </c>
       <c r="C40">
-        <v>103.105</v>
+        <v>102.509</v>
       </c>
       <c r="D40">
-        <v>103.101</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -4513,13 +4513,13 @@
         <v>39</v>
       </c>
       <c r="B41">
-        <v>21.34</v>
+        <v>21.39</v>
       </c>
       <c r="C41">
-        <v>103.105</v>
+        <v>102.509</v>
       </c>
       <c r="D41">
-        <v>103.06399999999999</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -4527,13 +4527,13 @@
         <v>40</v>
       </c>
       <c r="B42">
-        <v>21.36</v>
+        <v>21.39</v>
       </c>
       <c r="C42">
-        <v>103.105</v>
+        <v>102.509</v>
       </c>
       <c r="D42">
-        <v>103.06399999999999</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -4541,13 +4541,13 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>21.34</v>
+        <v>21.39</v>
       </c>
       <c r="C43">
-        <v>103.105</v>
+        <v>102.509</v>
       </c>
       <c r="D43">
-        <v>103.06399999999999</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -4555,13 +4555,13 @@
         <v>42</v>
       </c>
       <c r="B44">
-        <v>21.36</v>
+        <v>21.39</v>
       </c>
       <c r="C44">
-        <v>103.142</v>
+        <v>102.509</v>
       </c>
       <c r="D44">
-        <v>103.06399999999999</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -4569,13 +4569,13 @@
         <v>43</v>
       </c>
       <c r="B45">
-        <v>21.34</v>
+        <v>21.44</v>
       </c>
       <c r="C45">
-        <v>103.105</v>
+        <v>102.54600000000001</v>
       </c>
       <c r="D45">
-        <v>103.101</v>
+        <v>102.468</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -4583,13 +4583,13 @@
         <v>44</v>
       </c>
       <c r="B46">
-        <v>21.36</v>
+        <v>21.44</v>
       </c>
       <c r="C46">
-        <v>103.105</v>
+        <v>102.509</v>
       </c>
       <c r="D46">
-        <v>103.06399999999999</v>
+        <v>102.468</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -4597,13 +4597,13 @@
         <v>45</v>
       </c>
       <c r="B47">
-        <v>21.34</v>
+        <v>21.41</v>
       </c>
       <c r="C47">
-        <v>103.105</v>
+        <v>102.47199999999999</v>
       </c>
       <c r="D47">
-        <v>103.06399999999999</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -4611,13 +4611,13 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>21.36</v>
+        <v>21.44</v>
       </c>
       <c r="C48">
-        <v>103.142</v>
+        <v>102.509</v>
       </c>
       <c r="D48">
-        <v>103.101</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -4625,13 +4625,13 @@
         <v>47</v>
       </c>
       <c r="B49">
-        <v>21.36</v>
+        <v>21.39</v>
       </c>
       <c r="C49">
-        <v>103.105</v>
+        <v>102.509</v>
       </c>
       <c r="D49">
-        <v>103.06399999999999</v>
+        <v>102.468</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -4639,13 +4639,13 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>21.39</v>
+        <v>21.41</v>
       </c>
       <c r="C50">
-        <v>103.105</v>
+        <v>102.509</v>
       </c>
       <c r="D50">
-        <v>103.06399999999999</v>
+        <v>102.505</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -4653,13 +4653,13 @@
         <v>49</v>
       </c>
       <c r="B51">
-        <v>21.36</v>
+        <v>21.41</v>
       </c>
       <c r="C51">
-        <v>103.105</v>
+        <v>102.54600000000001</v>
       </c>
       <c r="D51">
-        <v>103.06399999999999</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -4667,13 +4667,13 @@
         <v>50</v>
       </c>
       <c r="B52">
-        <v>21.36</v>
+        <v>21.44</v>
       </c>
       <c r="C52">
-        <v>103.105</v>
+        <v>102.509</v>
       </c>
       <c r="D52">
-        <v>103.026</v>
+        <v>102.468</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -4681,13 +4681,13 @@
         <v>51</v>
       </c>
       <c r="B53">
-        <v>21.34</v>
+        <v>21.44</v>
       </c>
       <c r="C53">
-        <v>103.142</v>
+        <v>102.54600000000001</v>
       </c>
       <c r="D53">
-        <v>103.06399999999999</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -4695,13 +4695,13 @@
         <v>52</v>
       </c>
       <c r="B54">
-        <v>21.39</v>
+        <v>21.46</v>
       </c>
       <c r="C54">
-        <v>103.105</v>
+        <v>102.54600000000001</v>
       </c>
       <c r="D54">
-        <v>103.026</v>
+        <v>102.505</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -4709,13 +4709,13 @@
         <v>53</v>
       </c>
       <c r="B55">
-        <v>21.36</v>
+        <v>21.41</v>
       </c>
       <c r="C55">
-        <v>103.105</v>
+        <v>102.54600000000001</v>
       </c>
       <c r="D55">
-        <v>103.06399999999999</v>
+        <v>102.468</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -4723,13 +4723,13 @@
         <v>54</v>
       </c>
       <c r="B56">
-        <v>21.39</v>
+        <v>21.44</v>
       </c>
       <c r="C56">
-        <v>103.105</v>
+        <v>102.54600000000001</v>
       </c>
       <c r="D56">
-        <v>103.06399999999999</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -4737,13 +4737,13 @@
         <v>55</v>
       </c>
       <c r="B57">
-        <v>21.36</v>
+        <v>21.44</v>
       </c>
       <c r="C57">
-        <v>103.105</v>
+        <v>102.509</v>
       </c>
       <c r="D57">
-        <v>103.06399999999999</v>
+        <v>102.431</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -4751,13 +4751,13 @@
         <v>56</v>
       </c>
       <c r="B58">
-        <v>21.39</v>
+        <v>21.46</v>
       </c>
       <c r="C58">
-        <v>103.105</v>
+        <v>102.509</v>
       </c>
       <c r="D58">
-        <v>103.06399999999999</v>
+        <v>102.468</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -4765,13 +4765,13 @@
         <v>57</v>
       </c>
       <c r="B59">
-        <v>21.34</v>
+        <v>21.41</v>
       </c>
       <c r="C59">
-        <v>103.105</v>
+        <v>102.509</v>
       </c>
       <c r="D59">
-        <v>103.06399999999999</v>
+        <v>102.468</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -4779,13 +4779,13 @@
         <v>58</v>
       </c>
       <c r="B60">
-        <v>21.36</v>
+        <v>21.46</v>
       </c>
       <c r="C60">
-        <v>103.105</v>
+        <v>103.85</v>
       </c>
       <c r="D60">
-        <v>103.06399999999999</v>
+        <v>103.73399999999999</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -4793,13 +4793,13 @@
         <v>59</v>
       </c>
       <c r="B61">
-        <v>21.34</v>
+        <v>21.59</v>
       </c>
       <c r="C61">
-        <v>103.142</v>
+        <v>105.786</v>
       </c>
       <c r="D61">
-        <v>103.101</v>
+        <v>105.744</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -4807,13 +4807,13 @@
         <v>60</v>
       </c>
       <c r="B62">
-        <v>21.34</v>
+        <v>21.84</v>
       </c>
       <c r="C62">
-        <v>103.105</v>
+        <v>107.79600000000001</v>
       </c>
       <c r="D62">
-        <v>103.06399999999999</v>
+        <v>107.718</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -4821,13 +4821,13 @@
         <v>61</v>
       </c>
       <c r="B63">
-        <v>21.36</v>
+        <v>22.25</v>
       </c>
       <c r="C63">
-        <v>103.105</v>
+        <v>109.733</v>
       </c>
       <c r="D63">
-        <v>103.101</v>
+        <v>109.691</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -4835,13 +4835,13 @@
         <v>62</v>
       </c>
       <c r="B64">
-        <v>21.36</v>
+        <v>22.86</v>
       </c>
       <c r="C64">
-        <v>103.105</v>
+        <v>111.63200000000001</v>
       </c>
       <c r="D64">
-        <v>103.06399999999999</v>
+        <v>111.59</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -4849,13 +4849,13 @@
         <v>63</v>
       </c>
       <c r="B65">
-        <v>21.34</v>
+        <v>23.42</v>
       </c>
       <c r="C65">
-        <v>103.142</v>
+        <v>112.227</v>
       </c>
       <c r="D65">
-        <v>103.101</v>
+        <v>112.18600000000001</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -4863,13 +4863,13 @@
         <v>64</v>
       </c>
       <c r="B66">
-        <v>21.36</v>
+        <v>23.75</v>
       </c>
       <c r="C66">
-        <v>103.105</v>
+        <v>111.818</v>
       </c>
       <c r="D66">
-        <v>103.101</v>
+        <v>111.776</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -4877,13 +4877,13 @@
         <v>65</v>
       </c>
       <c r="B67">
-        <v>21.36</v>
+        <v>24.03</v>
       </c>
       <c r="C67">
-        <v>103.105</v>
+        <v>111.52</v>
       </c>
       <c r="D67">
-        <v>103.06399999999999</v>
+        <v>111.51600000000001</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -4891,13 +4891,13 @@
         <v>66</v>
       </c>
       <c r="B68">
-        <v>21.36</v>
+        <v>24.18</v>
       </c>
       <c r="C68">
-        <v>103.105</v>
+        <v>111.29600000000001</v>
       </c>
       <c r="D68">
-        <v>103.026</v>
+        <v>111.255</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -4905,13 +4905,13 @@
         <v>67</v>
       </c>
       <c r="B69">
-        <v>21.36</v>
+        <v>24.33</v>
       </c>
       <c r="C69">
-        <v>103.105</v>
+        <v>111.11</v>
       </c>
       <c r="D69">
-        <v>103.026</v>
+        <v>111.032</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -4919,13 +4919,13 @@
         <v>68</v>
       </c>
       <c r="B70">
-        <v>21.36</v>
+        <v>24.4</v>
       </c>
       <c r="C70">
-        <v>103.105</v>
+        <v>110.92400000000001</v>
       </c>
       <c r="D70">
-        <v>103.06399999999999</v>
+        <v>110.92</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -4933,13 +4933,13 @@
         <v>69</v>
       </c>
       <c r="B71">
-        <v>21.36</v>
+        <v>24.4</v>
       </c>
       <c r="C71">
-        <v>103.105</v>
+        <v>110.812</v>
       </c>
       <c r="D71">
-        <v>103.06399999999999</v>
+        <v>110.73399999999999</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -4947,13 +4947,13 @@
         <v>70</v>
       </c>
       <c r="B72">
-        <v>21.34</v>
+        <v>24.48</v>
       </c>
       <c r="C72">
-        <v>103.105</v>
+        <v>110.70099999999999</v>
       </c>
       <c r="D72">
-        <v>103.06399999999999</v>
+        <v>110.697</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -4961,13 +4961,13 @@
         <v>71</v>
       </c>
       <c r="B73">
-        <v>21.39</v>
+        <v>24.48</v>
       </c>
       <c r="C73">
-        <v>103.589</v>
+        <v>110.589</v>
       </c>
       <c r="D73">
-        <v>103.58499999999999</v>
+        <v>110.58499999999999</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -4975,13 +4975,13 @@
         <v>72</v>
       </c>
       <c r="B74">
-        <v>21.44</v>
+        <v>24.46</v>
       </c>
       <c r="C74">
-        <v>104.557</v>
+        <v>110.515</v>
       </c>
       <c r="D74">
-        <v>104.47799999999999</v>
+        <v>110.473</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -4989,13 +4989,13 @@
         <v>73</v>
       </c>
       <c r="B75">
-        <v>21.49</v>
+        <v>24.46</v>
       </c>
       <c r="C75">
-        <v>105.562</v>
+        <v>110.44</v>
       </c>
       <c r="D75">
-        <v>105.521</v>
+        <v>110.399</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -5003,13 +5003,13 @@
         <v>74</v>
       </c>
       <c r="B76">
-        <v>21.67</v>
+        <v>24.43</v>
       </c>
       <c r="C76">
-        <v>106.791</v>
+        <v>110.366</v>
       </c>
       <c r="D76">
-        <v>106.75</v>
+        <v>110.324</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -5017,13 +5017,13 @@
         <v>75</v>
       </c>
       <c r="B77">
-        <v>21.95</v>
+        <v>24.35</v>
       </c>
       <c r="C77">
-        <v>107.983</v>
+        <v>110.291</v>
       </c>
       <c r="D77">
-        <v>107.941</v>
+        <v>110.25</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -5031,13 +5031,13 @@
         <v>76</v>
       </c>
       <c r="B78">
-        <v>22.25</v>
+        <v>24.3</v>
       </c>
       <c r="C78">
-        <v>109.062</v>
+        <v>110.291</v>
       </c>
       <c r="D78">
-        <v>109.021</v>
+        <v>110.21299999999999</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -5045,13 +5045,13 @@
         <v>77</v>
       </c>
       <c r="B79">
-        <v>22.56</v>
+        <v>24.25</v>
       </c>
       <c r="C79">
-        <v>106.94</v>
+        <v>110.179</v>
       </c>
       <c r="D79">
-        <v>106.899</v>
+        <v>110.13800000000001</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -5059,13 +5059,13 @@
         <v>78</v>
       </c>
       <c r="B80">
-        <v>22.51</v>
+        <v>24.18</v>
       </c>
       <c r="C80">
-        <v>104.52</v>
+        <v>110.142</v>
       </c>
       <c r="D80">
-        <v>104.441</v>
+        <v>110.06399999999999</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -5073,13 +5073,13 @@
         <v>79</v>
       </c>
       <c r="B81">
-        <v>22.35</v>
+        <v>24.13</v>
       </c>
       <c r="C81">
-        <v>103.328</v>
+        <v>110.142</v>
       </c>
       <c r="D81">
-        <v>103.28700000000001</v>
+        <v>110.06399999999999</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -5087,13 +5087,13 @@
         <v>80</v>
       </c>
       <c r="B82">
-        <v>22.12</v>
+        <v>24.08</v>
       </c>
       <c r="C82">
-        <v>102.435</v>
+        <v>110.068</v>
       </c>
       <c r="D82">
-        <v>102.431</v>
+        <v>110.026</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -5101,13 +5101,13 @@
         <v>81</v>
       </c>
       <c r="B83">
-        <v>21.87</v>
+        <v>24</v>
       </c>
       <c r="C83">
-        <v>102.211</v>
+        <v>109.99299999999999</v>
       </c>
       <c r="D83">
-        <v>102.133</v>
+        <v>109.952</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -5115,13 +5115,13 @@
         <v>82</v>
       </c>
       <c r="B84">
-        <v>21.67</v>
+        <v>23.9</v>
       </c>
       <c r="C84">
-        <v>102.286</v>
+        <v>109.99299999999999</v>
       </c>
       <c r="D84">
-        <v>102.244</v>
+        <v>109.91500000000001</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -5129,13 +5129,13 @@
         <v>83</v>
       </c>
       <c r="B85">
-        <v>21.49</v>
+        <v>23.85</v>
       </c>
       <c r="C85">
-        <v>102.32299999999999</v>
+        <v>109.919</v>
       </c>
       <c r="D85">
-        <v>102.282</v>
+        <v>109.91500000000001</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -5143,13 +5143,13 @@
         <v>84</v>
       </c>
       <c r="B86">
-        <v>21.41</v>
+        <v>23.8</v>
       </c>
       <c r="C86">
-        <v>102.435</v>
+        <v>109.919</v>
       </c>
       <c r="D86">
-        <v>102.393</v>
+        <v>109.877</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -5157,13 +5157,13 @@
         <v>85</v>
       </c>
       <c r="B87">
-        <v>21.36</v>
+        <v>23.75</v>
       </c>
       <c r="C87">
-        <v>102.47199999999999</v>
+        <v>109.88200000000001</v>
       </c>
       <c r="D87">
-        <v>102.393</v>
+        <v>109.84</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -5171,13 +5171,13 @@
         <v>86</v>
       </c>
       <c r="B88">
-        <v>21.31</v>
+        <v>23.67</v>
       </c>
       <c r="C88">
-        <v>102.509</v>
+        <v>109.84399999999999</v>
       </c>
       <c r="D88">
-        <v>102.468</v>
+        <v>109.803</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -5185,13 +5185,13 @@
         <v>87</v>
       </c>
       <c r="B89">
-        <v>21.28</v>
+        <v>23.62</v>
       </c>
       <c r="C89">
-        <v>102.584</v>
+        <v>109.84399999999999</v>
       </c>
       <c r="D89">
-        <v>102.505</v>
+        <v>109.76600000000001</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -5199,13 +5199,13 @@
         <v>88</v>
       </c>
       <c r="B90">
-        <v>21.23</v>
+        <v>23.54</v>
       </c>
       <c r="C90">
-        <v>102.1</v>
+        <v>109.807</v>
       </c>
       <c r="D90">
-        <v>102.095</v>
+        <v>109.76600000000001</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
@@ -5213,13 +5213,13 @@
         <v>89</v>
       </c>
       <c r="B91">
-        <v>21.13</v>
+        <v>23.49</v>
       </c>
       <c r="C91">
-        <v>102.17400000000001</v>
+        <v>109.77</v>
       </c>
       <c r="D91">
-        <v>102.133</v>
+        <v>109.72799999999999</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -5227,13 +5227,13 @@
         <v>90</v>
       </c>
       <c r="B92">
-        <v>21.13</v>
+        <v>23.42</v>
       </c>
       <c r="C92">
-        <v>102.249</v>
+        <v>109.77</v>
       </c>
       <c r="D92">
-        <v>102.20699999999999</v>
+        <v>109.691</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -5241,13 +5241,13 @@
         <v>91</v>
       </c>
       <c r="B93">
-        <v>21.11</v>
+        <v>23.39</v>
       </c>
       <c r="C93">
-        <v>102.32299999999999</v>
+        <v>109.77</v>
       </c>
       <c r="D93">
-        <v>102.20699999999999</v>
+        <v>109.691</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -5255,13 +5255,13 @@
         <v>92</v>
       </c>
       <c r="B94">
-        <v>21.11</v>
+        <v>23.32</v>
       </c>
       <c r="C94">
-        <v>102.36</v>
+        <v>109.733</v>
       </c>
       <c r="D94">
-        <v>102.244</v>
+        <v>109.691</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -5269,13 +5269,13 @@
         <v>93</v>
       </c>
       <c r="B95">
-        <v>21.08</v>
+        <v>23.27</v>
       </c>
       <c r="C95">
-        <v>102.36</v>
+        <v>109.69499999999999</v>
       </c>
       <c r="D95">
-        <v>102.282</v>
+        <v>109.691</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -5283,13 +5283,13 @@
         <v>94</v>
       </c>
       <c r="B96">
-        <v>21.11</v>
+        <v>23.19</v>
       </c>
       <c r="C96">
-        <v>102.398</v>
+        <v>109.69499999999999</v>
       </c>
       <c r="D96">
-        <v>102.35599999999999</v>
+        <v>109.691</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -5297,13 +5297,13 @@
         <v>95</v>
       </c>
       <c r="B97">
-        <v>21.11</v>
+        <v>23.14</v>
       </c>
       <c r="C97">
-        <v>102.435</v>
+        <v>109.658</v>
       </c>
       <c r="D97">
-        <v>102.393</v>
+        <v>109.654</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
@@ -5311,13 +5311,13 @@
         <v>96</v>
       </c>
       <c r="B98">
-        <v>21.08</v>
+        <v>23.09</v>
       </c>
       <c r="C98">
-        <v>102.47199999999999</v>
+        <v>109.658</v>
       </c>
       <c r="D98">
-        <v>102.431</v>
+        <v>109.654</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -5325,13 +5325,13 @@
         <v>97</v>
       </c>
       <c r="B99">
-        <v>21.11</v>
+        <v>22.99</v>
       </c>
       <c r="C99">
-        <v>102.435</v>
+        <v>109.658</v>
       </c>
       <c r="D99">
-        <v>102.393</v>
+        <v>109.654</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -5339,13 +5339,13 @@
         <v>98</v>
       </c>
       <c r="B100">
-        <v>21.11</v>
+        <v>22.96</v>
       </c>
       <c r="C100">
-        <v>102.1</v>
+        <v>109.658</v>
       </c>
       <c r="D100">
-        <v>102.095</v>
+        <v>109.654</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
@@ -5353,13 +5353,13 @@
         <v>99</v>
       </c>
       <c r="B101">
-        <v>21.13</v>
+        <v>22.91</v>
       </c>
       <c r="C101">
-        <v>102.137</v>
+        <v>109.621</v>
       </c>
       <c r="D101">
-        <v>102.05800000000001</v>
+        <v>109.617</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -5367,13 +5367,13 @@
         <v>100</v>
       </c>
       <c r="B102">
-        <v>21.08</v>
+        <v>22.86</v>
       </c>
       <c r="C102">
-        <v>102.17400000000001</v>
+        <v>109.621</v>
       </c>
       <c r="D102">
-        <v>102.095</v>
+        <v>109.58</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -5381,13 +5381,13 @@
         <v>101</v>
       </c>
       <c r="B103">
-        <v>21.11</v>
+        <v>22.84</v>
       </c>
       <c r="C103">
-        <v>102.211</v>
+        <v>109.621</v>
       </c>
       <c r="D103">
-        <v>102.133</v>
+        <v>109.58</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -5395,13 +5395,13 @@
         <v>102</v>
       </c>
       <c r="B104">
-        <v>21.11</v>
+        <v>22.78</v>
       </c>
       <c r="C104">
-        <v>102.211</v>
+        <v>109.621</v>
       </c>
       <c r="D104">
-        <v>102.17</v>
+        <v>109.542</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -5409,13 +5409,13 @@
         <v>103</v>
       </c>
       <c r="B105">
-        <v>21.08</v>
+        <v>22.68</v>
       </c>
       <c r="C105">
-        <v>102.249</v>
+        <v>109.584</v>
       </c>
       <c r="D105">
-        <v>102.17</v>
+        <v>109.58</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -5423,13 +5423,13 @@
         <v>104</v>
       </c>
       <c r="B106">
-        <v>21.11</v>
+        <v>22.66</v>
       </c>
       <c r="C106">
-        <v>102.286</v>
+        <v>109.584</v>
       </c>
       <c r="D106">
-        <v>102.20699999999999</v>
+        <v>109.58</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
@@ -5437,13 +5437,13 @@
         <v>105</v>
       </c>
       <c r="B107">
-        <v>21.11</v>
+        <v>22.61</v>
       </c>
       <c r="C107">
-        <v>102.286</v>
+        <v>109.584</v>
       </c>
       <c r="D107">
-        <v>102.244</v>
+        <v>109.58</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -5451,13 +5451,13 @@
         <v>106</v>
       </c>
       <c r="B108">
-        <v>21.13</v>
+        <v>22.58</v>
       </c>
       <c r="C108">
-        <v>102.249</v>
+        <v>109.584</v>
       </c>
       <c r="D108">
-        <v>102.244</v>
+        <v>109.542</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
@@ -5465,13 +5465,13 @@
         <v>107</v>
       </c>
       <c r="B109">
-        <v>21.16</v>
+        <v>22.56</v>
       </c>
       <c r="C109">
-        <v>102.32299999999999</v>
+        <v>109.584</v>
       </c>
       <c r="D109">
-        <v>102.282</v>
+        <v>109.505</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
@@ -5479,13 +5479,13 @@
         <v>108</v>
       </c>
       <c r="B110">
-        <v>21.18</v>
+        <v>22.51</v>
       </c>
       <c r="C110">
-        <v>102.32299999999999</v>
+        <v>109.54600000000001</v>
       </c>
       <c r="D110">
-        <v>102.282</v>
+        <v>109.505</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
@@ -5493,13 +5493,13 @@
         <v>109</v>
       </c>
       <c r="B111">
-        <v>21.18</v>
+        <v>22.45</v>
       </c>
       <c r="C111">
-        <v>102.36</v>
+        <v>109.54600000000001</v>
       </c>
       <c r="D111">
-        <v>102.282</v>
+        <v>109.505</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
@@ -5507,13 +5507,13 @@
         <v>110</v>
       </c>
       <c r="B112">
-        <v>21.18</v>
+        <v>22.45</v>
       </c>
       <c r="C112">
-        <v>102.32299999999999</v>
+        <v>109.54600000000001</v>
       </c>
       <c r="D112">
-        <v>102.35599999999999</v>
+        <v>109.542</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
@@ -5521,13 +5521,13 @@
         <v>111</v>
       </c>
       <c r="B113">
-        <v>21.21</v>
+        <v>22.38</v>
       </c>
       <c r="C113">
-        <v>102.36</v>
+        <v>109.54600000000001</v>
       </c>
       <c r="D113">
-        <v>102.319</v>
+        <v>109.505</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
@@ -5535,13 +5535,13 @@
         <v>112</v>
       </c>
       <c r="B114">
-        <v>21.23</v>
+        <v>22.35</v>
       </c>
       <c r="C114">
-        <v>102.36</v>
+        <v>109.509</v>
       </c>
       <c r="D114">
-        <v>102.319</v>
+        <v>109.468</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
@@ -5549,13 +5549,13 @@
         <v>113</v>
       </c>
       <c r="B115">
-        <v>21.23</v>
+        <v>22.33</v>
       </c>
       <c r="C115">
-        <v>102.36</v>
+        <v>109.509</v>
       </c>
       <c r="D115">
-        <v>102.319</v>
+        <v>109.505</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
@@ -5563,13 +5563,13 @@
         <v>114</v>
       </c>
       <c r="B116">
-        <v>21.23</v>
+        <v>22.33</v>
       </c>
       <c r="C116">
-        <v>102.398</v>
+        <v>109.509</v>
       </c>
       <c r="D116">
-        <v>102.35599999999999</v>
+        <v>109.505</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
@@ -5577,13 +5577,13 @@
         <v>115</v>
       </c>
       <c r="B117">
-        <v>21.28</v>
+        <v>22.25</v>
       </c>
       <c r="C117">
-        <v>102.398</v>
+        <v>109.47199999999999</v>
       </c>
       <c r="D117">
-        <v>102.35599999999999</v>
+        <v>109.468</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
@@ -5591,13 +5591,13 @@
         <v>116</v>
       </c>
       <c r="B118">
-        <v>21.23</v>
+        <v>22.23</v>
       </c>
       <c r="C118">
-        <v>102.47199999999999</v>
+        <v>109.47199999999999</v>
       </c>
       <c r="D118">
-        <v>102.35599999999999</v>
+        <v>109.468</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
@@ -5605,13 +5605,13 @@
         <v>117</v>
       </c>
       <c r="B119">
-        <v>21.26</v>
+        <v>22.18</v>
       </c>
       <c r="C119">
-        <v>102.36</v>
+        <v>109.435</v>
       </c>
       <c r="D119">
-        <v>102.35599999999999</v>
+        <v>109.505</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
@@ -5619,13 +5619,13 @@
         <v>118</v>
       </c>
       <c r="B120">
-        <v>21.28</v>
+        <v>22.18</v>
       </c>
       <c r="C120">
-        <v>102.435</v>
+        <v>109.47199999999999</v>
       </c>
       <c r="D120">
-        <v>102.393</v>
+        <v>109.468</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
@@ -5633,13 +5633,13 @@
         <v>119</v>
       </c>
       <c r="B121">
-        <v>21.31</v>
+        <v>22.12</v>
       </c>
       <c r="C121">
-        <v>102.398</v>
+        <v>109.509</v>
       </c>
       <c r="D121">
-        <v>102.393</v>
+        <v>109.468</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
@@ -5647,13 +5647,13 @@
         <v>120</v>
       </c>
       <c r="B122">
-        <v>21.31</v>
+        <v>22.12</v>
       </c>
       <c r="C122">
-        <v>102.435</v>
+        <v>109.47199999999999</v>
       </c>
       <c r="D122">
-        <v>102.393</v>
+        <v>109.431</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -5661,13 +5661,13 @@
         <v>121</v>
       </c>
       <c r="B123">
-        <v>21.28</v>
+        <v>22.1</v>
       </c>
       <c r="C123">
-        <v>102.435</v>
+        <v>109.47199999999999</v>
       </c>
       <c r="D123">
-        <v>102.431</v>
+        <v>109.431</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
@@ -5675,13 +5675,13 @@
         <v>122</v>
       </c>
       <c r="B124">
-        <v>21.31</v>
+        <v>22.05</v>
       </c>
       <c r="C124">
-        <v>102.47199999999999</v>
+        <v>109.47199999999999</v>
       </c>
       <c r="D124">
-        <v>102.35599999999999</v>
+        <v>109.431</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
@@ -5689,13 +5689,13 @@
         <v>123</v>
       </c>
       <c r="B125">
-        <v>21.34</v>
+        <v>22.02</v>
       </c>
       <c r="C125">
-        <v>102.47199999999999</v>
+        <v>109.435</v>
       </c>
       <c r="D125">
-        <v>102.393</v>
+        <v>109.468</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
@@ -5703,13 +5703,13 @@
         <v>124</v>
       </c>
       <c r="B126">
-        <v>21.31</v>
+        <v>22</v>
       </c>
       <c r="C126">
-        <v>102.47199999999999</v>
+        <v>109.47199999999999</v>
       </c>
       <c r="D126">
-        <v>102.393</v>
+        <v>109.431</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
@@ -5717,13 +5717,13 @@
         <v>125</v>
       </c>
       <c r="B127">
-        <v>21.34</v>
+        <v>22</v>
       </c>
       <c r="C127">
-        <v>102.47199999999999</v>
+        <v>109.435</v>
       </c>
       <c r="D127">
-        <v>102.431</v>
+        <v>109.393</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
@@ -5731,13 +5731,13 @@
         <v>126</v>
       </c>
       <c r="B128">
-        <v>21.34</v>
+        <v>22</v>
       </c>
       <c r="C128">
-        <v>102.509</v>
+        <v>109.435</v>
       </c>
       <c r="D128">
-        <v>102.431</v>
+        <v>109.393</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
@@ -5745,13 +5745,13 @@
         <v>127</v>
       </c>
       <c r="B129">
-        <v>21.34</v>
+        <v>21.95</v>
       </c>
       <c r="C129">
-        <v>102.509</v>
+        <v>109.435</v>
       </c>
       <c r="D129">
-        <v>102.431</v>
+        <v>109.431</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
@@ -5759,13 +5759,13 @@
         <v>128</v>
       </c>
       <c r="B130">
-        <v>21.36</v>
+        <v>21.97</v>
       </c>
       <c r="C130">
-        <v>102.47199999999999</v>
+        <v>109.435</v>
       </c>
       <c r="D130">
-        <v>102.468</v>
+        <v>109.431</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
@@ -5773,13 +5773,13 @@
         <v>129</v>
       </c>
       <c r="B131">
-        <v>21.34</v>
+        <v>21.9</v>
       </c>
       <c r="C131">
-        <v>102.509</v>
+        <v>109.435</v>
       </c>
       <c r="D131">
-        <v>102.468</v>
+        <v>109.393</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
@@ -5787,13 +5787,13 @@
         <v>130</v>
       </c>
       <c r="B132">
-        <v>21.36</v>
+        <v>21.9</v>
       </c>
       <c r="C132">
-        <v>102.509</v>
+        <v>109.435</v>
       </c>
       <c r="D132">
-        <v>102.431</v>
+        <v>109.431</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
@@ -5801,13 +5801,13 @@
         <v>131</v>
       </c>
       <c r="B133">
-        <v>21.39</v>
+        <v>21.9</v>
       </c>
       <c r="C133">
-        <v>102.47199999999999</v>
+        <v>109.398</v>
       </c>
       <c r="D133">
-        <v>102.468</v>
+        <v>109.393</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
@@ -5815,13 +5815,13 @@
         <v>132</v>
       </c>
       <c r="B134">
-        <v>21.39</v>
+        <v>21.82</v>
       </c>
       <c r="C134">
-        <v>102.509</v>
+        <v>109.435</v>
       </c>
       <c r="D134">
-        <v>102.431</v>
+        <v>109.431</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
@@ -5829,13 +5829,13 @@
         <v>133</v>
       </c>
       <c r="B135">
-        <v>21.36</v>
+        <v>21.82</v>
       </c>
       <c r="C135">
-        <v>102.509</v>
+        <v>109.398</v>
       </c>
       <c r="D135">
-        <v>102.431</v>
+        <v>109.393</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
@@ -5843,13 +5843,13 @@
         <v>134</v>
       </c>
       <c r="B136">
-        <v>21.36</v>
+        <v>21.82</v>
       </c>
       <c r="C136">
-        <v>102.509</v>
+        <v>109.398</v>
       </c>
       <c r="D136">
-        <v>102.468</v>
+        <v>109.35599999999999</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
@@ -5857,13 +5857,13 @@
         <v>135</v>
       </c>
       <c r="B137">
-        <v>21.36</v>
+        <v>21.79</v>
       </c>
       <c r="C137">
-        <v>102.54600000000001</v>
+        <v>109.398</v>
       </c>
       <c r="D137">
-        <v>102.431</v>
+        <v>109.393</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
@@ -5871,13 +5871,13 @@
         <v>136</v>
       </c>
       <c r="B138">
-        <v>21.39</v>
+        <v>21.79</v>
       </c>
       <c r="C138">
-        <v>102.54600000000001</v>
+        <v>109.435</v>
       </c>
       <c r="D138">
-        <v>102.468</v>
+        <v>109.393</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
@@ -5885,13 +5885,13 @@
         <v>137</v>
       </c>
       <c r="B139">
-        <v>21.41</v>
+        <v>21.82</v>
       </c>
       <c r="C139">
-        <v>102.509</v>
+        <v>109.398</v>
       </c>
       <c r="D139">
-        <v>102.468</v>
+        <v>109.393</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
@@ -5899,13 +5899,13 @@
         <v>138</v>
       </c>
       <c r="B140">
-        <v>21.41</v>
+        <v>21.79</v>
       </c>
       <c r="C140">
-        <v>102.509</v>
+        <v>109.398</v>
       </c>
       <c r="D140">
-        <v>102.431</v>
+        <v>109.35599999999999</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
@@ -5913,13 +5913,13 @@
         <v>139</v>
       </c>
       <c r="B141">
-        <v>21.39</v>
+        <v>21.74</v>
       </c>
       <c r="C141">
-        <v>102.509</v>
+        <v>109.398</v>
       </c>
       <c r="D141">
-        <v>102.431</v>
+        <v>109.35599999999999</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
@@ -5927,13 +5927,13 @@
         <v>140</v>
       </c>
       <c r="B142">
-        <v>21.39</v>
+        <v>21.77</v>
       </c>
       <c r="C142">
-        <v>102.509</v>
+        <v>109.36</v>
       </c>
       <c r="D142">
-        <v>102.431</v>
+        <v>109.35599999999999</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
@@ -5941,13 +5941,13 @@
         <v>141</v>
       </c>
       <c r="B143">
-        <v>21.39</v>
+        <v>21.74</v>
       </c>
       <c r="C143">
-        <v>102.509</v>
+        <v>109.398</v>
       </c>
       <c r="D143">
-        <v>102.431</v>
+        <v>109.35599999999999</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
@@ -5955,13 +5955,13 @@
         <v>142</v>
       </c>
       <c r="B144">
-        <v>21.39</v>
+        <v>21.72</v>
       </c>
       <c r="C144">
-        <v>102.509</v>
+        <v>109.36</v>
       </c>
       <c r="D144">
-        <v>102.431</v>
+        <v>109.35599999999999</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
@@ -5969,13 +5969,13 @@
         <v>143</v>
       </c>
       <c r="B145">
-        <v>21.44</v>
+        <v>21.74</v>
       </c>
       <c r="C145">
-        <v>102.54600000000001</v>
+        <v>109.398</v>
       </c>
       <c r="D145">
-        <v>102.468</v>
+        <v>109.35599999999999</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
@@ -5983,13 +5983,13 @@
         <v>144</v>
       </c>
       <c r="B146">
-        <v>21.44</v>
+        <v>21.72</v>
       </c>
       <c r="C146">
-        <v>102.509</v>
+        <v>109.36</v>
       </c>
       <c r="D146">
-        <v>102.468</v>
+        <v>109.35599999999999</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
@@ -5997,13 +5997,13 @@
         <v>145</v>
       </c>
       <c r="B147">
-        <v>21.41</v>
+        <v>21.72</v>
       </c>
       <c r="C147">
-        <v>102.47199999999999</v>
+        <v>109.36</v>
       </c>
       <c r="D147">
-        <v>102.431</v>
+        <v>109.35599999999999</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
@@ -6011,13 +6011,13 @@
         <v>146</v>
       </c>
       <c r="B148">
-        <v>21.44</v>
+        <v>21.72</v>
       </c>
       <c r="C148">
-        <v>102.509</v>
+        <v>109.36</v>
       </c>
       <c r="D148">
-        <v>102.431</v>
+        <v>109.319</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
@@ -6025,13 +6025,13 @@
         <v>147</v>
       </c>
       <c r="B149">
-        <v>21.39</v>
+        <v>21.67</v>
       </c>
       <c r="C149">
-        <v>102.509</v>
+        <v>109.36</v>
       </c>
       <c r="D149">
-        <v>102.468</v>
+        <v>109.319</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
@@ -6039,13 +6039,13 @@
         <v>148</v>
       </c>
       <c r="B150">
-        <v>21.41</v>
+        <v>21.67</v>
       </c>
       <c r="C150">
-        <v>102.509</v>
+        <v>109.398</v>
       </c>
       <c r="D150">
-        <v>102.505</v>
+        <v>109.35599999999999</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
@@ -6053,13 +6053,13 @@
         <v>149</v>
       </c>
       <c r="B151">
-        <v>21.41</v>
+        <v>21.67</v>
       </c>
       <c r="C151">
-        <v>102.54600000000001</v>
+        <v>109.32299999999999</v>
       </c>
       <c r="D151">
-        <v>102.431</v>
+        <v>109.35599999999999</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
@@ -6067,13 +6067,13 @@
         <v>150</v>
       </c>
       <c r="B152">
-        <v>21.44</v>
+        <v>21.67</v>
       </c>
       <c r="C152">
-        <v>102.509</v>
+        <v>109.32299999999999</v>
       </c>
       <c r="D152">
-        <v>102.468</v>
+        <v>109.319</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
@@ -6081,13 +6081,13 @@
         <v>151</v>
       </c>
       <c r="B153">
-        <v>21.44</v>
+        <v>21.64</v>
       </c>
       <c r="C153">
-        <v>102.54600000000001</v>
+        <v>109.36</v>
       </c>
       <c r="D153">
-        <v>102.431</v>
+        <v>109.35599999999999</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
@@ -6095,13 +6095,13 @@
         <v>152</v>
       </c>
       <c r="B154">
-        <v>21.46</v>
+        <v>21.67</v>
       </c>
       <c r="C154">
-        <v>102.54600000000001</v>
+        <v>109.32299999999999</v>
       </c>
       <c r="D154">
-        <v>102.505</v>
+        <v>109.319</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
@@ -6109,13 +6109,13 @@
         <v>153</v>
       </c>
       <c r="B155">
-        <v>21.41</v>
+        <v>21.62</v>
       </c>
       <c r="C155">
-        <v>102.54600000000001</v>
+        <v>109.32299999999999</v>
       </c>
       <c r="D155">
-        <v>102.468</v>
+        <v>109.35599999999999</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
@@ -6123,13 +6123,13 @@
         <v>154</v>
       </c>
       <c r="B156">
-        <v>21.44</v>
+        <v>21.62</v>
       </c>
       <c r="C156">
-        <v>102.54600000000001</v>
+        <v>109.32299999999999</v>
       </c>
       <c r="D156">
-        <v>102.431</v>
+        <v>109.319</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
@@ -6137,13 +6137,13 @@
         <v>155</v>
       </c>
       <c r="B157">
-        <v>21.44</v>
+        <v>21.59</v>
       </c>
       <c r="C157">
-        <v>102.509</v>
+        <v>109.32299999999999</v>
       </c>
       <c r="D157">
-        <v>102.431</v>
+        <v>109.319</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
@@ -6151,13 +6151,13 @@
         <v>156</v>
       </c>
       <c r="B158">
-        <v>21.46</v>
+        <v>21.62</v>
       </c>
       <c r="C158">
-        <v>102.509</v>
+        <v>109.36</v>
       </c>
       <c r="D158">
-        <v>102.468</v>
+        <v>109.319</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
@@ -6165,13 +6165,13 @@
         <v>157</v>
       </c>
       <c r="B159">
-        <v>21.41</v>
+        <v>21.62</v>
       </c>
       <c r="C159">
-        <v>102.509</v>
+        <v>109.32299999999999</v>
       </c>
       <c r="D159">
-        <v>102.468</v>
+        <v>109.319</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
@@ -6179,13 +6179,13 @@
         <v>158</v>
       </c>
       <c r="B160">
-        <v>21.46</v>
+        <v>21.62</v>
       </c>
       <c r="C160">
-        <v>103.85</v>
+        <v>109.32299999999999</v>
       </c>
       <c r="D160">
-        <v>103.73399999999999</v>
+        <v>109.319</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
@@ -6193,13 +6193,13 @@
         <v>159</v>
       </c>
       <c r="B161">
-        <v>21.59</v>
+        <v>21.56</v>
       </c>
       <c r="C161">
-        <v>105.786</v>
+        <v>109.36</v>
       </c>
       <c r="D161">
-        <v>105.744</v>
+        <v>109.319</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
@@ -6207,13 +6207,13 @@
         <v>160</v>
       </c>
       <c r="B162">
-        <v>21.84</v>
+        <v>21.59</v>
       </c>
       <c r="C162">
-        <v>107.79600000000001</v>
+        <v>109.286</v>
       </c>
       <c r="D162">
-        <v>107.718</v>
+        <v>109.319</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
@@ -6221,13 +6221,13 @@
         <v>161</v>
       </c>
       <c r="B163">
-        <v>22.25</v>
+        <v>21.59</v>
       </c>
       <c r="C163">
-        <v>109.733</v>
+        <v>109.286</v>
       </c>
       <c r="D163">
-        <v>109.691</v>
+        <v>109.319</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
@@ -6235,13 +6235,13 @@
         <v>162</v>
       </c>
       <c r="B164">
-        <v>22.86</v>
+        <v>21.59</v>
       </c>
       <c r="C164">
-        <v>111.63200000000001</v>
+        <v>109.32299999999999</v>
       </c>
       <c r="D164">
-        <v>111.59</v>
+        <v>109.319</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
@@ -6249,13 +6249,13 @@
         <v>163</v>
       </c>
       <c r="B165">
-        <v>23.42</v>
+        <v>21.56</v>
       </c>
       <c r="C165">
-        <v>112.227</v>
+        <v>109.286</v>
       </c>
       <c r="D165">
-        <v>112.18600000000001</v>
+        <v>109.319</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
@@ -6263,13 +6263,13 @@
         <v>164</v>
       </c>
       <c r="B166">
-        <v>23.75</v>
+        <v>21.56</v>
       </c>
       <c r="C166">
-        <v>111.818</v>
+        <v>109.32299999999999</v>
       </c>
       <c r="D166">
-        <v>111.776</v>
+        <v>109.319</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
@@ -6277,13 +6277,13 @@
         <v>165</v>
       </c>
       <c r="B167">
-        <v>24.03</v>
+        <v>21.59</v>
       </c>
       <c r="C167">
-        <v>111.52</v>
+        <v>109.286</v>
       </c>
       <c r="D167">
-        <v>111.51600000000001</v>
+        <v>109.282</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
@@ -6291,13 +6291,13 @@
         <v>166</v>
       </c>
       <c r="B168">
-        <v>24.18</v>
+        <v>21.56</v>
       </c>
       <c r="C168">
-        <v>111.29600000000001</v>
+        <v>109.286</v>
       </c>
       <c r="D168">
-        <v>111.255</v>
+        <v>109.282</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
@@ -6305,13 +6305,13 @@
         <v>167</v>
       </c>
       <c r="B169">
-        <v>24.33</v>
+        <v>21.54</v>
       </c>
       <c r="C169">
-        <v>111.11</v>
+        <v>109.32299999999999</v>
       </c>
       <c r="D169">
-        <v>111.032</v>
+        <v>109.282</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
@@ -6319,13 +6319,13 @@
         <v>168</v>
       </c>
       <c r="B170">
-        <v>24.4</v>
+        <v>21.54</v>
       </c>
       <c r="C170">
-        <v>110.92400000000001</v>
+        <v>109.286</v>
       </c>
       <c r="D170">
-        <v>110.92</v>
+        <v>109.244</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
@@ -6333,13 +6333,13 @@
         <v>169</v>
       </c>
       <c r="B171">
-        <v>24.4</v>
+        <v>21.54</v>
       </c>
       <c r="C171">
-        <v>110.812</v>
+        <v>109.286</v>
       </c>
       <c r="D171">
-        <v>110.73399999999999</v>
+        <v>109.282</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
@@ -6347,13 +6347,13 @@
         <v>170</v>
       </c>
       <c r="B172">
-        <v>24.48</v>
+        <v>21.54</v>
       </c>
       <c r="C172">
-        <v>110.70099999999999</v>
+        <v>109.286</v>
       </c>
       <c r="D172">
-        <v>110.697</v>
+        <v>109.244</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
@@ -6361,13 +6361,13 @@
         <v>171</v>
       </c>
       <c r="B173">
-        <v>24.48</v>
+        <v>21.54</v>
       </c>
       <c r="C173">
-        <v>110.589</v>
+        <v>109.286</v>
       </c>
       <c r="D173">
-        <v>110.58499999999999</v>
+        <v>109.282</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
@@ -6375,13 +6375,13 @@
         <v>172</v>
       </c>
       <c r="B174">
-        <v>24.46</v>
+        <v>21.56</v>
       </c>
       <c r="C174">
-        <v>110.515</v>
+        <v>109.286</v>
       </c>
       <c r="D174">
-        <v>110.473</v>
+        <v>109.244</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
@@ -6389,13 +6389,13 @@
         <v>173</v>
       </c>
       <c r="B175">
-        <v>24.46</v>
+        <v>21.54</v>
       </c>
       <c r="C175">
-        <v>110.44</v>
+        <v>109.286</v>
       </c>
       <c r="D175">
-        <v>110.399</v>
+        <v>109.244</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
@@ -6403,13 +6403,13 @@
         <v>174</v>
       </c>
       <c r="B176">
-        <v>24.43</v>
+        <v>21.54</v>
       </c>
       <c r="C176">
-        <v>110.366</v>
+        <v>109.286</v>
       </c>
       <c r="D176">
-        <v>110.324</v>
+        <v>109.244</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
@@ -6417,13 +6417,13 @@
         <v>175</v>
       </c>
       <c r="B177">
-        <v>24.35</v>
+        <v>21.56</v>
       </c>
       <c r="C177">
-        <v>110.291</v>
+        <v>109.286</v>
       </c>
       <c r="D177">
-        <v>110.25</v>
+        <v>109.244</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
@@ -6431,13 +6431,13 @@
         <v>176</v>
       </c>
       <c r="B178">
-        <v>24.3</v>
+        <v>21.54</v>
       </c>
       <c r="C178">
-        <v>110.291</v>
+        <v>109.286</v>
       </c>
       <c r="D178">
-        <v>110.21299999999999</v>
+        <v>109.244</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
@@ -6445,13 +6445,13 @@
         <v>177</v>
       </c>
       <c r="B179">
-        <v>24.25</v>
+        <v>21.54</v>
       </c>
       <c r="C179">
-        <v>110.179</v>
+        <v>109.286</v>
       </c>
       <c r="D179">
-        <v>110.13800000000001</v>
+        <v>109.244</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
@@ -6459,13 +6459,13 @@
         <v>178</v>
       </c>
       <c r="B180">
-        <v>24.18</v>
+        <v>21.56</v>
       </c>
       <c r="C180">
-        <v>110.142</v>
+        <v>109.286</v>
       </c>
       <c r="D180">
-        <v>110.06399999999999</v>
+        <v>109.282</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
@@ -6473,13 +6473,13 @@
         <v>179</v>
       </c>
       <c r="B181">
-        <v>24.13</v>
+        <v>21.56</v>
       </c>
       <c r="C181">
-        <v>110.142</v>
+        <v>109.286</v>
       </c>
       <c r="D181">
-        <v>110.06399999999999</v>
+        <v>109.244</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
@@ -6487,13 +6487,13 @@
         <v>180</v>
       </c>
       <c r="B182">
-        <v>24.08</v>
+        <v>21.54</v>
       </c>
       <c r="C182">
-        <v>110.068</v>
+        <v>109.286</v>
       </c>
       <c r="D182">
-        <v>110.026</v>
+        <v>109.244</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
@@ -6501,13 +6501,13 @@
         <v>181</v>
       </c>
       <c r="B183">
-        <v>24</v>
+        <v>21.51</v>
       </c>
       <c r="C183">
-        <v>109.99299999999999</v>
+        <v>109.211</v>
       </c>
       <c r="D183">
-        <v>109.952</v>
+        <v>109.20699999999999</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
@@ -6515,13 +6515,13 @@
         <v>182</v>
       </c>
       <c r="B184">
-        <v>23.9</v>
+        <v>21.51</v>
       </c>
       <c r="C184">
-        <v>109.99299999999999</v>
+        <v>109.249</v>
       </c>
       <c r="D184">
-        <v>109.91500000000001</v>
+        <v>109.20699999999999</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
@@ -6529,13 +6529,13 @@
         <v>183</v>
       </c>
       <c r="B185">
-        <v>23.85</v>
+        <v>21.26</v>
       </c>
       <c r="C185">
-        <v>109.919</v>
+        <v>102.17400000000001</v>
       </c>
       <c r="D185">
-        <v>109.91500000000001</v>
+        <v>102.05800000000001</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
@@ -6543,13 +6543,13 @@
         <v>184</v>
       </c>
       <c r="B186">
-        <v>23.8</v>
+        <v>20.75</v>
       </c>
       <c r="C186">
-        <v>109.919</v>
+        <v>102.36</v>
       </c>
       <c r="D186">
-        <v>109.877</v>
+        <v>102.319</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
@@ -6557,13 +6557,13 @@
         <v>185</v>
       </c>
       <c r="B187">
-        <v>23.75</v>
+        <v>20.54</v>
       </c>
       <c r="C187">
-        <v>109.88200000000001</v>
+        <v>102.54600000000001</v>
       </c>
       <c r="D187">
-        <v>109.84</v>
+        <v>102.542</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
@@ -6571,13 +6571,13 @@
         <v>186</v>
       </c>
       <c r="B188">
-        <v>23.67</v>
+        <v>20.440000000000001</v>
       </c>
       <c r="C188">
-        <v>109.84399999999999</v>
+        <v>102.69499999999999</v>
       </c>
       <c r="D188">
-        <v>109.803</v>
+        <v>102.691</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
@@ -6585,13 +6585,13 @@
         <v>187</v>
       </c>
       <c r="B189">
-        <v>23.62</v>
+        <v>20.39</v>
       </c>
       <c r="C189">
-        <v>109.84399999999999</v>
+        <v>102.807</v>
       </c>
       <c r="D189">
-        <v>109.76600000000001</v>
+        <v>102.84</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
@@ -6599,13 +6599,13 @@
         <v>188</v>
       </c>
       <c r="B190">
-        <v>23.54</v>
+        <v>20.420000000000002</v>
       </c>
       <c r="C190">
-        <v>109.807</v>
+        <v>103.03</v>
       </c>
       <c r="D190">
-        <v>109.76600000000001</v>
+        <v>103.026</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
@@ -6613,13 +6613,13 @@
         <v>189</v>
       </c>
       <c r="B191">
-        <v>23.49</v>
+        <v>20.440000000000001</v>
       </c>
       <c r="C191">
-        <v>109.77</v>
+        <v>103.142</v>
       </c>
       <c r="D191">
-        <v>109.72799999999999</v>
+        <v>103.175</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
@@ -6627,13 +6627,13 @@
         <v>190</v>
       </c>
       <c r="B192">
-        <v>23.42</v>
+        <v>20.47</v>
       </c>
       <c r="C192">
-        <v>109.77</v>
+        <v>103.291</v>
       </c>
       <c r="D192">
-        <v>109.691</v>
+        <v>103.25</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
@@ -6641,13 +6641,13 @@
         <v>191</v>
       </c>
       <c r="B193">
-        <v>23.39</v>
+        <v>20.52</v>
       </c>
       <c r="C193">
-        <v>109.77</v>
+        <v>103.44</v>
       </c>
       <c r="D193">
-        <v>109.691</v>
+        <v>103.399</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
@@ -6655,13 +6655,13 @@
         <v>192</v>
       </c>
       <c r="B194">
-        <v>23.32</v>
+        <v>20.52</v>
       </c>
       <c r="C194">
-        <v>109.733</v>
+        <v>103.515</v>
       </c>
       <c r="D194">
-        <v>109.691</v>
+        <v>103.51</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
@@ -6669,13 +6669,13 @@
         <v>193</v>
       </c>
       <c r="B195">
-        <v>23.27</v>
+        <v>20.52</v>
       </c>
       <c r="C195">
-        <v>109.69499999999999</v>
+        <v>103.589</v>
       </c>
       <c r="D195">
-        <v>109.691</v>
+        <v>103.622</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
@@ -6683,13 +6683,13 @@
         <v>194</v>
       </c>
       <c r="B196">
-        <v>23.19</v>
+        <v>20.59</v>
       </c>
       <c r="C196">
-        <v>109.69499999999999</v>
+        <v>103.738</v>
       </c>
       <c r="D196">
-        <v>109.691</v>
+        <v>103.697</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
@@ -6697,13 +6697,13 @@
         <v>195</v>
       </c>
       <c r="B197">
-        <v>23.14</v>
+        <v>20.59</v>
       </c>
       <c r="C197">
-        <v>109.658</v>
+        <v>103.812</v>
       </c>
       <c r="D197">
-        <v>109.654</v>
+        <v>103.771</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
@@ -6711,13 +6711,13 @@
         <v>196</v>
       </c>
       <c r="B198">
-        <v>23.09</v>
+        <v>20.62</v>
       </c>
       <c r="C198">
-        <v>109.658</v>
+        <v>103.887</v>
       </c>
       <c r="D198">
-        <v>109.654</v>
+        <v>103.80800000000001</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
@@ -6725,13 +6725,13 @@
         <v>197</v>
       </c>
       <c r="B199">
-        <v>22.99</v>
+        <v>20.67</v>
       </c>
       <c r="C199">
-        <v>109.658</v>
+        <v>103.999</v>
       </c>
       <c r="D199">
-        <v>109.654</v>
+        <v>103.883</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
@@ -6739,13 +6739,13 @@
         <v>198</v>
       </c>
       <c r="B200">
-        <v>22.96</v>
+        <v>20.7</v>
       </c>
       <c r="C200">
-        <v>109.658</v>
+        <v>103.999</v>
       </c>
       <c r="D200">
-        <v>109.654</v>
+        <v>103.92</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
@@ -6753,13 +6753,13 @@
         <v>199</v>
       </c>
       <c r="B201">
-        <v>22.91</v>
+        <v>20.8</v>
       </c>
       <c r="C201">
-        <v>109.621</v>
+        <v>104.07299999999999</v>
       </c>
       <c r="D201">
-        <v>109.617</v>
+        <v>103.994</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
@@ -6767,13 +6767,13 @@
         <v>200</v>
       </c>
       <c r="B202">
-        <v>22.86</v>
+        <v>20.8</v>
       </c>
       <c r="C202">
-        <v>109.621</v>
+        <v>104.11</v>
       </c>
       <c r="D202">
-        <v>109.58</v>
+        <v>104.069</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
@@ -6781,13 +6781,13 @@
         <v>201</v>
       </c>
       <c r="B203">
-        <v>22.84</v>
+        <v>20.85</v>
       </c>
       <c r="C203">
-        <v>109.621</v>
+        <v>104.14700000000001</v>
       </c>
       <c r="D203">
-        <v>109.58</v>
+        <v>104.10599999999999</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
@@ -6795,13 +6795,13 @@
         <v>202</v>
       </c>
       <c r="B204">
-        <v>22.78</v>
+        <v>20.93</v>
       </c>
       <c r="C204">
-        <v>109.621</v>
+        <v>104.22199999999999</v>
       </c>
       <c r="D204">
-        <v>109.542</v>
+        <v>104.143</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
@@ -6809,13 +6809,13 @@
         <v>203</v>
       </c>
       <c r="B205">
-        <v>22.68</v>
+        <v>20.9</v>
       </c>
       <c r="C205">
-        <v>109.584</v>
+        <v>104.22199999999999</v>
       </c>
       <c r="D205">
-        <v>109.58</v>
+        <v>104.181</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
@@ -6823,13 +6823,13 @@
         <v>204</v>
       </c>
       <c r="B206">
-        <v>22.66</v>
+        <v>20.95</v>
       </c>
       <c r="C206">
-        <v>109.584</v>
+        <v>104.259</v>
       </c>
       <c r="D206">
-        <v>109.58</v>
+        <v>104.218</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
@@ -6837,13 +6837,13 @@
         <v>205</v>
       </c>
       <c r="B207">
-        <v>22.61</v>
+        <v>21</v>
       </c>
       <c r="C207">
-        <v>109.584</v>
+        <v>104.29600000000001</v>
       </c>
       <c r="D207">
-        <v>109.58</v>
+        <v>104.292</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
@@ -6851,13 +6851,13 @@
         <v>206</v>
       </c>
       <c r="B208">
-        <v>22.58</v>
+        <v>21.05</v>
       </c>
       <c r="C208">
-        <v>109.584</v>
+        <v>104.371</v>
       </c>
       <c r="D208">
-        <v>109.542</v>
+        <v>104.292</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
@@ -6865,13 +6865,13 @@
         <v>207</v>
       </c>
       <c r="B209">
-        <v>22.56</v>
+        <v>21.08</v>
       </c>
       <c r="C209">
-        <v>109.584</v>
+        <v>104.371</v>
       </c>
       <c r="D209">
-        <v>109.505</v>
+        <v>104.33</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
@@ -6879,13 +6879,13 @@
         <v>208</v>
       </c>
       <c r="B210">
-        <v>22.51</v>
+        <v>21.13</v>
       </c>
       <c r="C210">
-        <v>109.54600000000001</v>
+        <v>104.408</v>
       </c>
       <c r="D210">
-        <v>109.505</v>
+        <v>104.33</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
@@ -6893,13 +6893,13 @@
         <v>209</v>
       </c>
       <c r="B211">
-        <v>22.45</v>
+        <v>21.13</v>
       </c>
       <c r="C211">
-        <v>109.54600000000001</v>
+        <v>104.408</v>
       </c>
       <c r="D211">
-        <v>109.505</v>
+        <v>104.367</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
@@ -6907,13 +6907,13 @@
         <v>210</v>
       </c>
       <c r="B212">
-        <v>22.45</v>
+        <v>21.13</v>
       </c>
       <c r="C212">
-        <v>109.54600000000001</v>
+        <v>104.44499999999999</v>
       </c>
       <c r="D212">
-        <v>109.542</v>
+        <v>104.367</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
@@ -6921,13 +6921,13 @@
         <v>211</v>
       </c>
       <c r="B213">
-        <v>22.38</v>
+        <v>21.18</v>
       </c>
       <c r="C213">
-        <v>109.54600000000001</v>
+        <v>104.483</v>
       </c>
       <c r="D213">
-        <v>109.505</v>
+        <v>104.404</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
@@ -6935,13 +6935,13 @@
         <v>212</v>
       </c>
       <c r="B214">
-        <v>22.35</v>
+        <v>21.18</v>
       </c>
       <c r="C214">
-        <v>109.509</v>
+        <v>104.483</v>
       </c>
       <c r="D214">
-        <v>109.468</v>
+        <v>104.441</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
@@ -6949,13 +6949,13 @@
         <v>213</v>
       </c>
       <c r="B215">
-        <v>22.33</v>
+        <v>21.26</v>
       </c>
       <c r="C215">
-        <v>109.509</v>
+        <v>104.483</v>
       </c>
       <c r="D215">
-        <v>109.505</v>
+        <v>104.441</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
@@ -6963,13 +6963,13 @@
         <v>214</v>
       </c>
       <c r="B216">
-        <v>22.33</v>
+        <v>21.26</v>
       </c>
       <c r="C216">
-        <v>109.509</v>
+        <v>104.44499999999999</v>
       </c>
       <c r="D216">
-        <v>109.505</v>
+        <v>104.441</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
@@ -6977,13 +6977,13 @@
         <v>215</v>
       </c>
       <c r="B217">
-        <v>22.25</v>
+        <v>21.26</v>
       </c>
       <c r="C217">
-        <v>109.47199999999999</v>
+        <v>104.483</v>
       </c>
       <c r="D217">
-        <v>109.468</v>
+        <v>104.441</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
@@ -6991,13 +6991,13 @@
         <v>216</v>
       </c>
       <c r="B218">
-        <v>22.23</v>
+        <v>21.28</v>
       </c>
       <c r="C218">
-        <v>109.47199999999999</v>
+        <v>104.52</v>
       </c>
       <c r="D218">
-        <v>109.468</v>
+        <v>104.47799999999999</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
@@ -7005,13 +7005,13 @@
         <v>217</v>
       </c>
       <c r="B219">
-        <v>22.18</v>
+        <v>21.34</v>
       </c>
       <c r="C219">
-        <v>109.435</v>
+        <v>104.52</v>
       </c>
       <c r="D219">
-        <v>109.505</v>
+        <v>104.47799999999999</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
@@ -7019,13 +7019,13 @@
         <v>218</v>
       </c>
       <c r="B220">
-        <v>22.18</v>
+        <v>21.31</v>
       </c>
       <c r="C220">
-        <v>109.47199999999999</v>
+        <v>104.483</v>
       </c>
       <c r="D220">
-        <v>109.468</v>
+        <v>104.47799999999999</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
@@ -7033,13 +7033,13 @@
         <v>219</v>
       </c>
       <c r="B221">
-        <v>22.12</v>
+        <v>21.34</v>
       </c>
       <c r="C221">
-        <v>109.509</v>
+        <v>104.557</v>
       </c>
       <c r="D221">
-        <v>109.468</v>
+        <v>104.441</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
@@ -7047,13 +7047,13 @@
         <v>220</v>
       </c>
       <c r="B222">
-        <v>22.12</v>
+        <v>21.34</v>
       </c>
       <c r="C222">
-        <v>109.47199999999999</v>
+        <v>104.557</v>
       </c>
       <c r="D222">
-        <v>109.431</v>
+        <v>104.47799999999999</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
@@ -7061,13 +7061,13 @@
         <v>221</v>
       </c>
       <c r="B223">
-        <v>22.1</v>
+        <v>21.36</v>
       </c>
       <c r="C223">
-        <v>109.47199999999999</v>
+        <v>104.557</v>
       </c>
       <c r="D223">
-        <v>109.431</v>
+        <v>104.47799999999999</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
@@ -7075,13 +7075,13 @@
         <v>222</v>
       </c>
       <c r="B224">
-        <v>22.05</v>
+        <v>21.36</v>
       </c>
       <c r="C224">
-        <v>109.47199999999999</v>
+        <v>104.557</v>
       </c>
       <c r="D224">
-        <v>109.431</v>
+        <v>104.47799999999999</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
@@ -7089,13 +7089,13 @@
         <v>223</v>
       </c>
       <c r="B225">
-        <v>22.02</v>
+        <v>21.36</v>
       </c>
       <c r="C225">
-        <v>109.435</v>
+        <v>104.52</v>
       </c>
       <c r="D225">
-        <v>109.468</v>
+        <v>104.51600000000001</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
@@ -7103,13 +7103,13 @@
         <v>224</v>
       </c>
       <c r="B226">
-        <v>22</v>
+        <v>21.39</v>
       </c>
       <c r="C226">
-        <v>109.47199999999999</v>
+        <v>104.557</v>
       </c>
       <c r="D226">
-        <v>109.431</v>
+        <v>104.51600000000001</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
@@ -7117,13 +7117,13 @@
         <v>225</v>
       </c>
       <c r="B227">
-        <v>22</v>
+        <v>21.41</v>
       </c>
       <c r="C227">
-        <v>109.435</v>
+        <v>104.557</v>
       </c>
       <c r="D227">
-        <v>109.393</v>
+        <v>104.51600000000001</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
@@ -7131,13 +7131,13 @@
         <v>226</v>
       </c>
       <c r="B228">
-        <v>22</v>
+        <v>21.39</v>
       </c>
       <c r="C228">
-        <v>109.435</v>
+        <v>104.59399999999999</v>
       </c>
       <c r="D228">
-        <v>109.393</v>
+        <v>104.47799999999999</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
@@ -7145,13 +7145,13 @@
         <v>227</v>
       </c>
       <c r="B229">
-        <v>21.95</v>
+        <v>21.44</v>
       </c>
       <c r="C229">
-        <v>109.435</v>
+        <v>104.557</v>
       </c>
       <c r="D229">
-        <v>109.431</v>
+        <v>104.51600000000001</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
@@ -7159,13 +7159,13 @@
         <v>228</v>
       </c>
       <c r="B230">
-        <v>21.97</v>
+        <v>21.44</v>
       </c>
       <c r="C230">
-        <v>109.435</v>
+        <v>104.557</v>
       </c>
       <c r="D230">
-        <v>109.431</v>
+        <v>104.553</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
@@ -7173,13 +7173,13 @@
         <v>229</v>
       </c>
       <c r="B231">
-        <v>21.9</v>
+        <v>21.44</v>
       </c>
       <c r="C231">
-        <v>109.435</v>
+        <v>104.59399999999999</v>
       </c>
       <c r="D231">
-        <v>109.393</v>
+        <v>104.47799999999999</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
@@ -7187,13 +7187,13 @@
         <v>230</v>
       </c>
       <c r="B232">
-        <v>21.9</v>
+        <v>21.44</v>
       </c>
       <c r="C232">
-        <v>109.435</v>
+        <v>104.557</v>
       </c>
       <c r="D232">
-        <v>109.431</v>
+        <v>104.51600000000001</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
@@ -7201,13 +7201,13 @@
         <v>231</v>
       </c>
       <c r="B233">
-        <v>21.9</v>
+        <v>21.46</v>
       </c>
       <c r="C233">
-        <v>109.398</v>
+        <v>104.557</v>
       </c>
       <c r="D233">
-        <v>109.393</v>
+        <v>104.553</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
@@ -7215,13 +7215,13 @@
         <v>232</v>
       </c>
       <c r="B234">
-        <v>21.82</v>
+        <v>21.46</v>
       </c>
       <c r="C234">
-        <v>109.435</v>
+        <v>104.557</v>
       </c>
       <c r="D234">
-        <v>109.431</v>
+        <v>104.553</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
@@ -7229,13 +7229,13 @@
         <v>233</v>
       </c>
       <c r="B235">
-        <v>21.82</v>
+        <v>21.46</v>
       </c>
       <c r="C235">
-        <v>109.398</v>
+        <v>104.557</v>
       </c>
       <c r="D235">
-        <v>109.393</v>
+        <v>104.51600000000001</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
@@ -7243,13 +7243,13 @@
         <v>234</v>
       </c>
       <c r="B236">
-        <v>21.82</v>
+        <v>21.49</v>
       </c>
       <c r="C236">
-        <v>109.398</v>
+        <v>104.557</v>
       </c>
       <c r="D236">
-        <v>109.35599999999999</v>
+        <v>104.47799999999999</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
@@ -7257,13 +7257,13 @@
         <v>235</v>
       </c>
       <c r="B237">
-        <v>21.79</v>
+        <v>21.49</v>
       </c>
       <c r="C237">
-        <v>109.398</v>
+        <v>104.557</v>
       </c>
       <c r="D237">
-        <v>109.393</v>
+        <v>104.47799999999999</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
@@ -7271,13 +7271,13 @@
         <v>236</v>
       </c>
       <c r="B238">
-        <v>21.79</v>
+        <v>21.46</v>
       </c>
       <c r="C238">
-        <v>109.435</v>
+        <v>104.557</v>
       </c>
       <c r="D238">
-        <v>109.393</v>
+        <v>104.51600000000001</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
@@ -7285,13 +7285,13 @@
         <v>237</v>
       </c>
       <c r="B239">
-        <v>21.82</v>
+        <v>21.49</v>
       </c>
       <c r="C239">
-        <v>109.398</v>
+        <v>104.59399999999999</v>
       </c>
       <c r="D239">
-        <v>109.393</v>
+        <v>104.47799999999999</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
@@ -7299,13 +7299,13 @@
         <v>238</v>
       </c>
       <c r="B240">
-        <v>21.79</v>
+        <v>21.46</v>
       </c>
       <c r="C240">
-        <v>109.398</v>
+        <v>104.557</v>
       </c>
       <c r="D240">
-        <v>109.35599999999999</v>
+        <v>104.47799999999999</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
@@ -7313,13 +7313,13 @@
         <v>239</v>
       </c>
       <c r="B241">
-        <v>21.74</v>
+        <v>21.49</v>
       </c>
       <c r="C241">
-        <v>109.398</v>
+        <v>104.557</v>
       </c>
       <c r="D241">
-        <v>109.35599999999999</v>
+        <v>104.47799999999999</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
@@ -7327,13 +7327,13 @@
         <v>240</v>
       </c>
       <c r="B242">
-        <v>21.77</v>
+        <v>21.49</v>
       </c>
       <c r="C242">
-        <v>109.36</v>
+        <v>104.557</v>
       </c>
       <c r="D242">
-        <v>109.35599999999999</v>
+        <v>104.47799999999999</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
@@ -7341,13 +7341,13 @@
         <v>241</v>
       </c>
       <c r="B243">
-        <v>21.74</v>
+        <v>21.51</v>
       </c>
       <c r="C243">
-        <v>109.398</v>
+        <v>104.557</v>
       </c>
       <c r="D243">
-        <v>109.35599999999999</v>
+        <v>104.441</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
@@ -7355,13 +7355,13 @@
         <v>242</v>
       </c>
       <c r="B244">
-        <v>21.72</v>
+        <v>21.49</v>
       </c>
       <c r="C244">
-        <v>109.36</v>
+        <v>104.52</v>
       </c>
       <c r="D244">
-        <v>109.35599999999999</v>
+        <v>104.51600000000001</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
@@ -7369,13 +7369,13 @@
         <v>243</v>
       </c>
       <c r="B245">
-        <v>21.74</v>
+        <v>21.51</v>
       </c>
       <c r="C245">
-        <v>109.398</v>
+        <v>104.557</v>
       </c>
       <c r="D245">
-        <v>109.35599999999999</v>
+        <v>104.47799999999999</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
@@ -7383,13 +7383,13 @@
         <v>244</v>
       </c>
       <c r="B246">
-        <v>21.72</v>
+        <v>21.51</v>
       </c>
       <c r="C246">
-        <v>109.36</v>
+        <v>104.557</v>
       </c>
       <c r="D246">
-        <v>109.35599999999999</v>
+        <v>104.51600000000001</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
@@ -7397,13 +7397,13 @@
         <v>245</v>
       </c>
       <c r="B247">
-        <v>21.72</v>
+        <v>21.51</v>
       </c>
       <c r="C247">
-        <v>109.36</v>
+        <v>104.557</v>
       </c>
       <c r="D247">
-        <v>109.35599999999999</v>
+        <v>104.51600000000001</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
@@ -7411,1412 +7411,12 @@
         <v>246</v>
       </c>
       <c r="B248">
-        <v>21.72</v>
+        <v>21.49</v>
       </c>
       <c r="C248">
-        <v>109.36</v>
+        <v>104.557</v>
       </c>
       <c r="D248">
-        <v>109.319</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A249">
-        <v>247</v>
-      </c>
-      <c r="B249">
-        <v>21.67</v>
-      </c>
-      <c r="C249">
-        <v>109.36</v>
-      </c>
-      <c r="D249">
-        <v>109.319</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A250">
-        <v>248</v>
-      </c>
-      <c r="B250">
-        <v>21.67</v>
-      </c>
-      <c r="C250">
-        <v>109.398</v>
-      </c>
-      <c r="D250">
-        <v>109.35599999999999</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A251">
-        <v>249</v>
-      </c>
-      <c r="B251">
-        <v>21.67</v>
-      </c>
-      <c r="C251">
-        <v>109.32299999999999</v>
-      </c>
-      <c r="D251">
-        <v>109.35599999999999</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A252">
-        <v>250</v>
-      </c>
-      <c r="B252">
-        <v>21.67</v>
-      </c>
-      <c r="C252">
-        <v>109.32299999999999</v>
-      </c>
-      <c r="D252">
-        <v>109.319</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A253">
-        <v>251</v>
-      </c>
-      <c r="B253">
-        <v>21.64</v>
-      </c>
-      <c r="C253">
-        <v>109.36</v>
-      </c>
-      <c r="D253">
-        <v>109.35599999999999</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A254">
-        <v>252</v>
-      </c>
-      <c r="B254">
-        <v>21.67</v>
-      </c>
-      <c r="C254">
-        <v>109.32299999999999</v>
-      </c>
-      <c r="D254">
-        <v>109.319</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A255">
-        <v>253</v>
-      </c>
-      <c r="B255">
-        <v>21.62</v>
-      </c>
-      <c r="C255">
-        <v>109.32299999999999</v>
-      </c>
-      <c r="D255">
-        <v>109.35599999999999</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A256">
-        <v>254</v>
-      </c>
-      <c r="B256">
-        <v>21.62</v>
-      </c>
-      <c r="C256">
-        <v>109.32299999999999</v>
-      </c>
-      <c r="D256">
-        <v>109.319</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A257">
-        <v>255</v>
-      </c>
-      <c r="B257">
-        <v>21.59</v>
-      </c>
-      <c r="C257">
-        <v>109.32299999999999</v>
-      </c>
-      <c r="D257">
-        <v>109.319</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A258">
-        <v>256</v>
-      </c>
-      <c r="B258">
-        <v>21.62</v>
-      </c>
-      <c r="C258">
-        <v>109.36</v>
-      </c>
-      <c r="D258">
-        <v>109.319</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A259">
-        <v>257</v>
-      </c>
-      <c r="B259">
-        <v>21.62</v>
-      </c>
-      <c r="C259">
-        <v>109.32299999999999</v>
-      </c>
-      <c r="D259">
-        <v>109.319</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A260">
-        <v>258</v>
-      </c>
-      <c r="B260">
-        <v>21.62</v>
-      </c>
-      <c r="C260">
-        <v>109.32299999999999</v>
-      </c>
-      <c r="D260">
-        <v>109.319</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A261">
-        <v>259</v>
-      </c>
-      <c r="B261">
-        <v>21.56</v>
-      </c>
-      <c r="C261">
-        <v>109.36</v>
-      </c>
-      <c r="D261">
-        <v>109.319</v>
-      </c>
-    </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A262">
-        <v>260</v>
-      </c>
-      <c r="B262">
-        <v>21.59</v>
-      </c>
-      <c r="C262">
-        <v>109.286</v>
-      </c>
-      <c r="D262">
-        <v>109.319</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A263">
-        <v>261</v>
-      </c>
-      <c r="B263">
-        <v>21.59</v>
-      </c>
-      <c r="C263">
-        <v>109.286</v>
-      </c>
-      <c r="D263">
-        <v>109.319</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A264">
-        <v>262</v>
-      </c>
-      <c r="B264">
-        <v>21.59</v>
-      </c>
-      <c r="C264">
-        <v>109.32299999999999</v>
-      </c>
-      <c r="D264">
-        <v>109.319</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A265">
-        <v>263</v>
-      </c>
-      <c r="B265">
-        <v>21.56</v>
-      </c>
-      <c r="C265">
-        <v>109.286</v>
-      </c>
-      <c r="D265">
-        <v>109.319</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A266">
-        <v>264</v>
-      </c>
-      <c r="B266">
-        <v>21.56</v>
-      </c>
-      <c r="C266">
-        <v>109.32299999999999</v>
-      </c>
-      <c r="D266">
-        <v>109.319</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A267">
-        <v>265</v>
-      </c>
-      <c r="B267">
-        <v>21.59</v>
-      </c>
-      <c r="C267">
-        <v>109.286</v>
-      </c>
-      <c r="D267">
-        <v>109.282</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A268">
-        <v>266</v>
-      </c>
-      <c r="B268">
-        <v>21.56</v>
-      </c>
-      <c r="C268">
-        <v>109.286</v>
-      </c>
-      <c r="D268">
-        <v>109.282</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A269">
-        <v>267</v>
-      </c>
-      <c r="B269">
-        <v>21.54</v>
-      </c>
-      <c r="C269">
-        <v>109.32299999999999</v>
-      </c>
-      <c r="D269">
-        <v>109.282</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A270">
-        <v>268</v>
-      </c>
-      <c r="B270">
-        <v>21.54</v>
-      </c>
-      <c r="C270">
-        <v>109.286</v>
-      </c>
-      <c r="D270">
-        <v>109.244</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A271">
-        <v>269</v>
-      </c>
-      <c r="B271">
-        <v>21.54</v>
-      </c>
-      <c r="C271">
-        <v>109.286</v>
-      </c>
-      <c r="D271">
-        <v>109.282</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A272">
-        <v>270</v>
-      </c>
-      <c r="B272">
-        <v>21.54</v>
-      </c>
-      <c r="C272">
-        <v>109.286</v>
-      </c>
-      <c r="D272">
-        <v>109.244</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A273">
-        <v>271</v>
-      </c>
-      <c r="B273">
-        <v>21.54</v>
-      </c>
-      <c r="C273">
-        <v>109.286</v>
-      </c>
-      <c r="D273">
-        <v>109.282</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A274">
-        <v>272</v>
-      </c>
-      <c r="B274">
-        <v>21.56</v>
-      </c>
-      <c r="C274">
-        <v>109.286</v>
-      </c>
-      <c r="D274">
-        <v>109.244</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A275">
-        <v>273</v>
-      </c>
-      <c r="B275">
-        <v>21.54</v>
-      </c>
-      <c r="C275">
-        <v>109.286</v>
-      </c>
-      <c r="D275">
-        <v>109.244</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A276">
-        <v>274</v>
-      </c>
-      <c r="B276">
-        <v>21.54</v>
-      </c>
-      <c r="C276">
-        <v>109.286</v>
-      </c>
-      <c r="D276">
-        <v>109.244</v>
-      </c>
-    </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A277">
-        <v>275</v>
-      </c>
-      <c r="B277">
-        <v>21.56</v>
-      </c>
-      <c r="C277">
-        <v>109.286</v>
-      </c>
-      <c r="D277">
-        <v>109.244</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A278">
-        <v>276</v>
-      </c>
-      <c r="B278">
-        <v>21.54</v>
-      </c>
-      <c r="C278">
-        <v>109.286</v>
-      </c>
-      <c r="D278">
-        <v>109.244</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A279">
-        <v>277</v>
-      </c>
-      <c r="B279">
-        <v>21.54</v>
-      </c>
-      <c r="C279">
-        <v>109.286</v>
-      </c>
-      <c r="D279">
-        <v>109.244</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A280">
-        <v>278</v>
-      </c>
-      <c r="B280">
-        <v>21.56</v>
-      </c>
-      <c r="C280">
-        <v>109.286</v>
-      </c>
-      <c r="D280">
-        <v>109.282</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A281">
-        <v>279</v>
-      </c>
-      <c r="B281">
-        <v>21.56</v>
-      </c>
-      <c r="C281">
-        <v>109.286</v>
-      </c>
-      <c r="D281">
-        <v>109.244</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A282">
-        <v>280</v>
-      </c>
-      <c r="B282">
-        <v>21.54</v>
-      </c>
-      <c r="C282">
-        <v>109.286</v>
-      </c>
-      <c r="D282">
-        <v>109.244</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A283">
-        <v>281</v>
-      </c>
-      <c r="B283">
-        <v>21.51</v>
-      </c>
-      <c r="C283">
-        <v>109.211</v>
-      </c>
-      <c r="D283">
-        <v>109.20699999999999</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A284">
-        <v>282</v>
-      </c>
-      <c r="B284">
-        <v>21.51</v>
-      </c>
-      <c r="C284">
-        <v>109.249</v>
-      </c>
-      <c r="D284">
-        <v>109.20699999999999</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A285">
-        <v>283</v>
-      </c>
-      <c r="B285">
-        <v>21.26</v>
-      </c>
-      <c r="C285">
-        <v>102.17400000000001</v>
-      </c>
-      <c r="D285">
-        <v>102.05800000000001</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A286">
-        <v>284</v>
-      </c>
-      <c r="B286">
-        <v>20.75</v>
-      </c>
-      <c r="C286">
-        <v>102.36</v>
-      </c>
-      <c r="D286">
-        <v>102.319</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A287">
-        <v>285</v>
-      </c>
-      <c r="B287">
-        <v>20.54</v>
-      </c>
-      <c r="C287">
-        <v>102.54600000000001</v>
-      </c>
-      <c r="D287">
-        <v>102.542</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A288">
-        <v>286</v>
-      </c>
-      <c r="B288">
-        <v>20.440000000000001</v>
-      </c>
-      <c r="C288">
-        <v>102.69499999999999</v>
-      </c>
-      <c r="D288">
-        <v>102.691</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A289">
-        <v>287</v>
-      </c>
-      <c r="B289">
-        <v>20.39</v>
-      </c>
-      <c r="C289">
-        <v>102.807</v>
-      </c>
-      <c r="D289">
-        <v>102.84</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A290">
-        <v>288</v>
-      </c>
-      <c r="B290">
-        <v>20.420000000000002</v>
-      </c>
-      <c r="C290">
-        <v>103.03</v>
-      </c>
-      <c r="D290">
-        <v>103.026</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A291">
-        <v>289</v>
-      </c>
-      <c r="B291">
-        <v>20.440000000000001</v>
-      </c>
-      <c r="C291">
-        <v>103.142</v>
-      </c>
-      <c r="D291">
-        <v>103.175</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A292">
-        <v>290</v>
-      </c>
-      <c r="B292">
-        <v>20.47</v>
-      </c>
-      <c r="C292">
-        <v>103.291</v>
-      </c>
-      <c r="D292">
-        <v>103.25</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A293">
-        <v>291</v>
-      </c>
-      <c r="B293">
-        <v>20.52</v>
-      </c>
-      <c r="C293">
-        <v>103.44</v>
-      </c>
-      <c r="D293">
-        <v>103.399</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A294">
-        <v>292</v>
-      </c>
-      <c r="B294">
-        <v>20.52</v>
-      </c>
-      <c r="C294">
-        <v>103.515</v>
-      </c>
-      <c r="D294">
-        <v>103.51</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A295">
-        <v>293</v>
-      </c>
-      <c r="B295">
-        <v>20.52</v>
-      </c>
-      <c r="C295">
-        <v>103.589</v>
-      </c>
-      <c r="D295">
-        <v>103.622</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A296">
-        <v>294</v>
-      </c>
-      <c r="B296">
-        <v>20.59</v>
-      </c>
-      <c r="C296">
-        <v>103.738</v>
-      </c>
-      <c r="D296">
-        <v>103.697</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A297">
-        <v>295</v>
-      </c>
-      <c r="B297">
-        <v>20.59</v>
-      </c>
-      <c r="C297">
-        <v>103.812</v>
-      </c>
-      <c r="D297">
-        <v>103.771</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A298">
-        <v>296</v>
-      </c>
-      <c r="B298">
-        <v>20.62</v>
-      </c>
-      <c r="C298">
-        <v>103.887</v>
-      </c>
-      <c r="D298">
-        <v>103.80800000000001</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A299">
-        <v>297</v>
-      </c>
-      <c r="B299">
-        <v>20.67</v>
-      </c>
-      <c r="C299">
-        <v>103.999</v>
-      </c>
-      <c r="D299">
-        <v>103.883</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A300">
-        <v>298</v>
-      </c>
-      <c r="B300">
-        <v>20.7</v>
-      </c>
-      <c r="C300">
-        <v>103.999</v>
-      </c>
-      <c r="D300">
-        <v>103.92</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A301">
-        <v>299</v>
-      </c>
-      <c r="B301">
-        <v>20.8</v>
-      </c>
-      <c r="C301">
-        <v>104.07299999999999</v>
-      </c>
-      <c r="D301">
-        <v>103.994</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A302">
-        <v>300</v>
-      </c>
-      <c r="B302">
-        <v>20.8</v>
-      </c>
-      <c r="C302">
-        <v>104.11</v>
-      </c>
-      <c r="D302">
-        <v>104.069</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A303">
-        <v>301</v>
-      </c>
-      <c r="B303">
-        <v>20.85</v>
-      </c>
-      <c r="C303">
-        <v>104.14700000000001</v>
-      </c>
-      <c r="D303">
-        <v>104.10599999999999</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A304">
-        <v>302</v>
-      </c>
-      <c r="B304">
-        <v>20.93</v>
-      </c>
-      <c r="C304">
-        <v>104.22199999999999</v>
-      </c>
-      <c r="D304">
-        <v>104.143</v>
-      </c>
-    </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A305">
-        <v>303</v>
-      </c>
-      <c r="B305">
-        <v>20.9</v>
-      </c>
-      <c r="C305">
-        <v>104.22199999999999</v>
-      </c>
-      <c r="D305">
-        <v>104.181</v>
-      </c>
-    </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A306">
-        <v>304</v>
-      </c>
-      <c r="B306">
-        <v>20.95</v>
-      </c>
-      <c r="C306">
-        <v>104.259</v>
-      </c>
-      <c r="D306">
-        <v>104.218</v>
-      </c>
-    </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A307">
-        <v>305</v>
-      </c>
-      <c r="B307">
-        <v>21</v>
-      </c>
-      <c r="C307">
-        <v>104.29600000000001</v>
-      </c>
-      <c r="D307">
-        <v>104.292</v>
-      </c>
-    </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A308">
-        <v>306</v>
-      </c>
-      <c r="B308">
-        <v>21.05</v>
-      </c>
-      <c r="C308">
-        <v>104.371</v>
-      </c>
-      <c r="D308">
-        <v>104.292</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A309">
-        <v>307</v>
-      </c>
-      <c r="B309">
-        <v>21.08</v>
-      </c>
-      <c r="C309">
-        <v>104.371</v>
-      </c>
-      <c r="D309">
-        <v>104.33</v>
-      </c>
-    </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A310">
-        <v>308</v>
-      </c>
-      <c r="B310">
-        <v>21.13</v>
-      </c>
-      <c r="C310">
-        <v>104.408</v>
-      </c>
-      <c r="D310">
-        <v>104.33</v>
-      </c>
-    </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A311">
-        <v>309</v>
-      </c>
-      <c r="B311">
-        <v>21.13</v>
-      </c>
-      <c r="C311">
-        <v>104.408</v>
-      </c>
-      <c r="D311">
-        <v>104.367</v>
-      </c>
-    </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A312">
-        <v>310</v>
-      </c>
-      <c r="B312">
-        <v>21.13</v>
-      </c>
-      <c r="C312">
-        <v>104.44499999999999</v>
-      </c>
-      <c r="D312">
-        <v>104.367</v>
-      </c>
-    </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A313">
-        <v>311</v>
-      </c>
-      <c r="B313">
-        <v>21.18</v>
-      </c>
-      <c r="C313">
-        <v>104.483</v>
-      </c>
-      <c r="D313">
-        <v>104.404</v>
-      </c>
-    </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A314">
-        <v>312</v>
-      </c>
-      <c r="B314">
-        <v>21.18</v>
-      </c>
-      <c r="C314">
-        <v>104.483</v>
-      </c>
-      <c r="D314">
-        <v>104.441</v>
-      </c>
-    </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A315">
-        <v>313</v>
-      </c>
-      <c r="B315">
-        <v>21.26</v>
-      </c>
-      <c r="C315">
-        <v>104.483</v>
-      </c>
-      <c r="D315">
-        <v>104.441</v>
-      </c>
-    </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A316">
-        <v>314</v>
-      </c>
-      <c r="B316">
-        <v>21.26</v>
-      </c>
-      <c r="C316">
-        <v>104.44499999999999</v>
-      </c>
-      <c r="D316">
-        <v>104.441</v>
-      </c>
-    </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A317">
-        <v>315</v>
-      </c>
-      <c r="B317">
-        <v>21.26</v>
-      </c>
-      <c r="C317">
-        <v>104.483</v>
-      </c>
-      <c r="D317">
-        <v>104.441</v>
-      </c>
-    </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A318">
-        <v>316</v>
-      </c>
-      <c r="B318">
-        <v>21.28</v>
-      </c>
-      <c r="C318">
-        <v>104.52</v>
-      </c>
-      <c r="D318">
-        <v>104.47799999999999</v>
-      </c>
-    </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A319">
-        <v>317</v>
-      </c>
-      <c r="B319">
-        <v>21.34</v>
-      </c>
-      <c r="C319">
-        <v>104.52</v>
-      </c>
-      <c r="D319">
-        <v>104.47799999999999</v>
-      </c>
-    </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A320">
-        <v>318</v>
-      </c>
-      <c r="B320">
-        <v>21.31</v>
-      </c>
-      <c r="C320">
-        <v>104.483</v>
-      </c>
-      <c r="D320">
-        <v>104.47799999999999</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A321">
-        <v>319</v>
-      </c>
-      <c r="B321">
-        <v>21.34</v>
-      </c>
-      <c r="C321">
-        <v>104.557</v>
-      </c>
-      <c r="D321">
-        <v>104.441</v>
-      </c>
-    </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A322">
-        <v>320</v>
-      </c>
-      <c r="B322">
-        <v>21.34</v>
-      </c>
-      <c r="C322">
-        <v>104.557</v>
-      </c>
-      <c r="D322">
-        <v>104.47799999999999</v>
-      </c>
-    </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A323">
-        <v>321</v>
-      </c>
-      <c r="B323">
-        <v>21.36</v>
-      </c>
-      <c r="C323">
-        <v>104.557</v>
-      </c>
-      <c r="D323">
-        <v>104.47799999999999</v>
-      </c>
-    </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A324">
-        <v>322</v>
-      </c>
-      <c r="B324">
-        <v>21.36</v>
-      </c>
-      <c r="C324">
-        <v>104.557</v>
-      </c>
-      <c r="D324">
-        <v>104.47799999999999</v>
-      </c>
-    </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A325">
-        <v>323</v>
-      </c>
-      <c r="B325">
-        <v>21.36</v>
-      </c>
-      <c r="C325">
-        <v>104.52</v>
-      </c>
-      <c r="D325">
-        <v>104.51600000000001</v>
-      </c>
-    </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A326">
-        <v>324</v>
-      </c>
-      <c r="B326">
-        <v>21.39</v>
-      </c>
-      <c r="C326">
-        <v>104.557</v>
-      </c>
-      <c r="D326">
-        <v>104.51600000000001</v>
-      </c>
-    </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A327">
-        <v>325</v>
-      </c>
-      <c r="B327">
-        <v>21.41</v>
-      </c>
-      <c r="C327">
-        <v>104.557</v>
-      </c>
-      <c r="D327">
-        <v>104.51600000000001</v>
-      </c>
-    </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A328">
-        <v>326</v>
-      </c>
-      <c r="B328">
-        <v>21.39</v>
-      </c>
-      <c r="C328">
-        <v>104.59399999999999</v>
-      </c>
-      <c r="D328">
-        <v>104.47799999999999</v>
-      </c>
-    </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A329">
-        <v>327</v>
-      </c>
-      <c r="B329">
-        <v>21.44</v>
-      </c>
-      <c r="C329">
-        <v>104.557</v>
-      </c>
-      <c r="D329">
-        <v>104.51600000000001</v>
-      </c>
-    </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A330">
-        <v>328</v>
-      </c>
-      <c r="B330">
-        <v>21.44</v>
-      </c>
-      <c r="C330">
-        <v>104.557</v>
-      </c>
-      <c r="D330">
-        <v>104.553</v>
-      </c>
-    </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A331">
-        <v>329</v>
-      </c>
-      <c r="B331">
-        <v>21.44</v>
-      </c>
-      <c r="C331">
-        <v>104.59399999999999</v>
-      </c>
-      <c r="D331">
-        <v>104.47799999999999</v>
-      </c>
-    </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A332">
-        <v>330</v>
-      </c>
-      <c r="B332">
-        <v>21.44</v>
-      </c>
-      <c r="C332">
-        <v>104.557</v>
-      </c>
-      <c r="D332">
-        <v>104.51600000000001</v>
-      </c>
-    </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A333">
-        <v>331</v>
-      </c>
-      <c r="B333">
-        <v>21.46</v>
-      </c>
-      <c r="C333">
-        <v>104.557</v>
-      </c>
-      <c r="D333">
-        <v>104.553</v>
-      </c>
-    </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A334">
-        <v>332</v>
-      </c>
-      <c r="B334">
-        <v>21.46</v>
-      </c>
-      <c r="C334">
-        <v>104.557</v>
-      </c>
-      <c r="D334">
-        <v>104.553</v>
-      </c>
-    </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A335">
-        <v>333</v>
-      </c>
-      <c r="B335">
-        <v>21.46</v>
-      </c>
-      <c r="C335">
-        <v>104.557</v>
-      </c>
-      <c r="D335">
-        <v>104.51600000000001</v>
-      </c>
-    </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A336">
-        <v>334</v>
-      </c>
-      <c r="B336">
-        <v>21.49</v>
-      </c>
-      <c r="C336">
-        <v>104.557</v>
-      </c>
-      <c r="D336">
-        <v>104.47799999999999</v>
-      </c>
-    </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A337">
-        <v>335</v>
-      </c>
-      <c r="B337">
-        <v>21.49</v>
-      </c>
-      <c r="C337">
-        <v>104.557</v>
-      </c>
-      <c r="D337">
-        <v>104.47799999999999</v>
-      </c>
-    </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A338">
-        <v>336</v>
-      </c>
-      <c r="B338">
-        <v>21.46</v>
-      </c>
-      <c r="C338">
-        <v>104.557</v>
-      </c>
-      <c r="D338">
-        <v>104.51600000000001</v>
-      </c>
-    </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A339">
-        <v>337</v>
-      </c>
-      <c r="B339">
-        <v>21.49</v>
-      </c>
-      <c r="C339">
-        <v>104.59399999999999</v>
-      </c>
-      <c r="D339">
-        <v>104.47799999999999</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A340">
-        <v>338</v>
-      </c>
-      <c r="B340">
-        <v>21.46</v>
-      </c>
-      <c r="C340">
-        <v>104.557</v>
-      </c>
-      <c r="D340">
-        <v>104.47799999999999</v>
-      </c>
-    </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A341">
-        <v>339</v>
-      </c>
-      <c r="B341">
-        <v>21.49</v>
-      </c>
-      <c r="C341">
-        <v>104.557</v>
-      </c>
-      <c r="D341">
-        <v>104.47799999999999</v>
-      </c>
-    </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A342">
-        <v>340</v>
-      </c>
-      <c r="B342">
-        <v>21.49</v>
-      </c>
-      <c r="C342">
-        <v>104.557</v>
-      </c>
-      <c r="D342">
-        <v>104.47799999999999</v>
-      </c>
-    </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A343">
-        <v>341</v>
-      </c>
-      <c r="B343">
-        <v>21.51</v>
-      </c>
-      <c r="C343">
-        <v>104.557</v>
-      </c>
-      <c r="D343">
-        <v>104.441</v>
-      </c>
-    </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A344">
-        <v>342</v>
-      </c>
-      <c r="B344">
-        <v>21.49</v>
-      </c>
-      <c r="C344">
-        <v>104.52</v>
-      </c>
-      <c r="D344">
-        <v>104.51600000000001</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A345">
-        <v>343</v>
-      </c>
-      <c r="B345">
-        <v>21.51</v>
-      </c>
-      <c r="C345">
-        <v>104.557</v>
-      </c>
-      <c r="D345">
-        <v>104.47799999999999</v>
-      </c>
-    </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A346">
-        <v>344</v>
-      </c>
-      <c r="B346">
-        <v>21.51</v>
-      </c>
-      <c r="C346">
-        <v>104.557</v>
-      </c>
-      <c r="D346">
-        <v>104.51600000000001</v>
-      </c>
-    </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A347">
-        <v>345</v>
-      </c>
-      <c r="B347">
-        <v>21.51</v>
-      </c>
-      <c r="C347">
-        <v>104.557</v>
-      </c>
-      <c r="D347">
-        <v>104.51600000000001</v>
-      </c>
-    </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A348">
-        <v>346</v>
-      </c>
-      <c r="B348">
-        <v>21.49</v>
-      </c>
-      <c r="C348">
-        <v>104.557</v>
-      </c>
-      <c r="D348">
         <v>104.51600000000001</v>
       </c>
     </row>
